--- a/pca-interpretable-clustering/classified_data/Other.xlsx
+++ b/pca-interpretable-clustering/classified_data/Other.xlsx
@@ -8823,7 +8823,7 @@
         <v>214.79968</v>
       </c>
       <c r="H2">
-        <v>676.4455400000001</v>
+        <v>676.4455367</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -8849,7 +8849,7 @@
         <v>199.53061</v>
       </c>
       <c r="H3">
-        <v>492.0689</v>
+        <v>492.068897</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8875,7 +8875,7 @@
         <v>209.78853</v>
       </c>
       <c r="H4">
-        <v>623.24988</v>
+        <v>623.249877</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -8901,7 +8901,7 @@
         <v>15.87414</v>
       </c>
       <c r="H5">
-        <v>118.8495</v>
+        <v>144.9250385</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -8927,7 +8927,7 @@
         <v>270.47758</v>
       </c>
       <c r="H6">
-        <v>714.706</v>
+        <v>714.7060028</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -8953,7 +8953,7 @@
         <v>45.27249</v>
       </c>
       <c r="H7">
-        <v>250.44428</v>
+        <v>250.4442832</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -8979,7 +8979,7 @@
         <v>15.6511</v>
       </c>
       <c r="H8">
-        <v>112.32919</v>
+        <v>112.3291874</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -9005,7 +9005,7 @@
         <v>16.96934</v>
       </c>
       <c r="H9">
-        <v>180.13251</v>
+        <v>180.1325092</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9031,7 +9031,7 @@
         <v>81.6168</v>
       </c>
       <c r="H10">
-        <v>354.38422</v>
+        <v>304.6871672</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -9057,7 +9057,7 @@
         <v>440.64664</v>
       </c>
       <c r="H11">
-        <v>1450.48083</v>
+        <v>1450.480826</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -9083,7 +9083,7 @@
         <v>87.98647</v>
       </c>
       <c r="H12">
-        <v>348.93685</v>
+        <v>348.936855</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -9109,7 +9109,7 @@
         <v>74.61749</v>
       </c>
       <c r="H13">
-        <v>284.63892</v>
+        <v>282.6915746</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -9135,7 +9135,7 @@
         <v>55.21792</v>
       </c>
       <c r="H14">
-        <v>299.61073</v>
+        <v>299.6107261</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -9161,7 +9161,7 @@
         <v>46.46777</v>
       </c>
       <c r="H15">
-        <v>221.46958</v>
+        <v>182.2834898</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -9187,7 +9187,7 @@
         <v>64.74334</v>
       </c>
       <c r="H16">
-        <v>512.39059</v>
+        <v>512.3905852</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -9213,7 +9213,7 @@
         <v>105.80563</v>
       </c>
       <c r="H17">
-        <v>380.95721</v>
+        <v>329.0431157</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -9239,7 +9239,7 @@
         <v>85.93195</v>
       </c>
       <c r="H18">
-        <v>270.69878</v>
+        <v>270.698779</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -9265,7 +9265,7 @@
         <v>47.53834</v>
       </c>
       <c r="H19">
-        <v>194.12876</v>
+        <v>194.128763</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -9291,7 +9291,7 @@
         <v>242.05975</v>
       </c>
       <c r="H20">
-        <v>377.60951</v>
+        <v>377.6095149</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -9317,7 +9317,7 @@
         <v>29.82883</v>
       </c>
       <c r="H21">
-        <v>182.65227</v>
+        <v>182.6522728</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -9343,7 +9343,7 @@
         <v>20.21053</v>
       </c>
       <c r="H22">
-        <v>251.96271</v>
+        <v>251.9627118</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -9369,7 +9369,7 @@
         <v>26.34548</v>
       </c>
       <c r="H23">
-        <v>306.99152</v>
+        <v>306.9915169</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -9395,7 +9395,7 @@
         <v>33.20224</v>
       </c>
       <c r="H24">
-        <v>157.25351</v>
+        <v>157.253512</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -9421,7 +9421,7 @@
         <v>21.33108</v>
       </c>
       <c r="H25">
-        <v>206.09361</v>
+        <v>206.093609</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -9447,7 +9447,7 @@
         <v>79.41424000000001</v>
       </c>
       <c r="H26">
-        <v>327.73101</v>
+        <v>259.8283995</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -9473,7 +9473,7 @@
         <v>203.32432</v>
       </c>
       <c r="H27">
-        <v>444.31497</v>
+        <v>444.3149712</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -9499,7 +9499,7 @@
         <v>210.69734</v>
       </c>
       <c r="H28">
-        <v>454.08509</v>
+        <v>454.0850852</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -9525,7 +9525,7 @@
         <v>28.02007</v>
       </c>
       <c r="H29">
-        <v>211.76376</v>
+        <v>211.7637592</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -9551,7 +9551,7 @@
         <v>27.85363</v>
       </c>
       <c r="H30">
-        <v>165.95637</v>
+        <v>165.9563713</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -9577,7 +9577,7 @@
         <v>14.75345</v>
       </c>
       <c r="H31">
-        <v>92.99056</v>
+        <v>92.99055946999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -9603,7 +9603,7 @@
         <v>31.5496</v>
       </c>
       <c r="H32">
-        <v>130.78559</v>
+        <v>130.7855872</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -9629,7 +9629,7 @@
         <v>12.63362</v>
       </c>
       <c r="H33">
-        <v>134.92099</v>
+        <v>134.9209857</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -9655,7 +9655,7 @@
         <v>62.74765</v>
       </c>
       <c r="H34">
-        <v>276.98791</v>
+        <v>276.9879077</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -9681,7 +9681,7 @@
         <v>73.54861</v>
       </c>
       <c r="H35">
-        <v>279.78444</v>
+        <v>279.7844354</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -9707,7 +9707,7 @@
         <v>52.76631</v>
       </c>
       <c r="H36">
-        <v>285.73701</v>
+        <v>285.7370113</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -9733,7 +9733,7 @@
         <v>53.93261</v>
       </c>
       <c r="H37">
-        <v>257.97333</v>
+        <v>194.6564512</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -9759,7 +9759,7 @@
         <v>149.62652</v>
       </c>
       <c r="H38">
-        <v>341.27622</v>
+        <v>341.2762211</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -9785,7 +9785,7 @@
         <v>329.01625</v>
       </c>
       <c r="H39">
-        <v>473.578</v>
+        <v>473.5779973</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -9811,7 +9811,7 @@
         <v>28.59847</v>
       </c>
       <c r="H40">
-        <v>170.71635</v>
+        <v>170.7163529</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -9837,7 +9837,7 @@
         <v>23.80765</v>
       </c>
       <c r="H41">
-        <v>131.9086</v>
+        <v>131.9085973</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -9863,7 +9863,7 @@
         <v>134.16452</v>
       </c>
       <c r="H42">
-        <v>469.26857</v>
+        <v>469.2685658</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -9889,7 +9889,7 @@
         <v>11.88968</v>
       </c>
       <c r="H43">
-        <v>128.52003</v>
+        <v>128.5200334</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -9915,7 +9915,7 @@
         <v>170.46461</v>
       </c>
       <c r="H44">
-        <v>534.62177</v>
+        <v>534.6217656</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -9941,7 +9941,7 @@
         <v>131.88572</v>
       </c>
       <c r="H45">
-        <v>371.54932</v>
+        <v>371.5493225</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -9967,7 +9967,7 @@
         <v>293.03526</v>
       </c>
       <c r="H46">
-        <v>714.4524699999999</v>
+        <v>714.4524729</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -9993,7 +9993,7 @@
         <v>11.11044</v>
       </c>
       <c r="H47">
-        <v>108.29424</v>
+        <v>175.3795606</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -10019,7 +10019,7 @@
         <v>2.53659</v>
       </c>
       <c r="H48">
-        <v>51.97021</v>
+        <v>51.97021497</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -10045,7 +10045,7 @@
         <v>72.25599</v>
       </c>
       <c r="H49">
-        <v>330.48645</v>
+        <v>343.6966028</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -10071,7 +10071,7 @@
         <v>32.76179</v>
       </c>
       <c r="H50">
-        <v>180.68697</v>
+        <v>180.6869655</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -10097,7 +10097,7 @@
         <v>295.33791</v>
       </c>
       <c r="H51">
-        <v>684.08794</v>
+        <v>643.0387596</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -10123,7 +10123,7 @@
         <v>129.37769</v>
       </c>
       <c r="H52">
-        <v>453.83536</v>
+        <v>453.8353614</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -10149,7 +10149,7 @@
         <v>274.91099</v>
       </c>
       <c r="H53">
-        <v>583.88512</v>
+        <v>511.4443124</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -10175,7 +10175,7 @@
         <v>227.87493</v>
       </c>
       <c r="H54">
-        <v>476.38006</v>
+        <v>476.3800558</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -10201,7 +10201,7 @@
         <v>74.73663999999999</v>
       </c>
       <c r="H55">
-        <v>248.14064</v>
+        <v>194.2882859</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -10227,7 +10227,7 @@
         <v>66.23923000000001</v>
       </c>
       <c r="H56">
-        <v>482.33808</v>
+        <v>482.3380757</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -10253,7 +10253,7 @@
         <v>91.55786000000001</v>
       </c>
       <c r="H57">
-        <v>471.79072</v>
+        <v>471.790722</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -10279,7 +10279,7 @@
         <v>42.52602</v>
       </c>
       <c r="H58">
-        <v>342.88813</v>
+        <v>342.8881304</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -10305,7 +10305,7 @@
         <v>77.64206</v>
       </c>
       <c r="H59">
-        <v>248.83655</v>
+        <v>192.108318</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -10331,7 +10331,7 @@
         <v>317.09754</v>
       </c>
       <c r="H60">
-        <v>499.07295</v>
+        <v>499.0729452</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -10357,7 +10357,7 @@
         <v>261.88916</v>
       </c>
       <c r="H61">
-        <v>560.83595</v>
+        <v>512.0639068</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -10383,7 +10383,7 @@
         <v>79.5543</v>
       </c>
       <c r="H62">
-        <v>248.95696</v>
+        <v>191.1382896</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -10409,7 +10409,7 @@
         <v>13.95226</v>
       </c>
       <c r="H63">
-        <v>115.00538</v>
+        <v>115.0053821</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -10435,7 +10435,7 @@
         <v>32.40486</v>
       </c>
       <c r="H64">
-        <v>164.66312</v>
+        <v>155.9183167</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -10461,7 +10461,7 @@
         <v>171.74664</v>
       </c>
       <c r="H65">
-        <v>707.80949</v>
+        <v>707.8094893</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -10487,7 +10487,7 @@
         <v>239.21916</v>
       </c>
       <c r="H66">
-        <v>677.80706</v>
+        <v>677.8070628</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -10513,7 +10513,7 @@
         <v>15.96338</v>
       </c>
       <c r="H67">
-        <v>140.60649</v>
+        <v>235.5999578</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -10539,7 +10539,7 @@
         <v>267.6726</v>
       </c>
       <c r="H68">
-        <v>709.44858</v>
+        <v>614.9752873</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -10565,7 +10565,7 @@
         <v>50.50133</v>
       </c>
       <c r="H69">
-        <v>222.4599</v>
+        <v>222.459899</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -10591,7 +10591,7 @@
         <v>88.51588</v>
       </c>
       <c r="H70">
-        <v>564.37602</v>
+        <v>564.3760172</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -10617,7 +10617,7 @@
         <v>234.33535</v>
       </c>
       <c r="H71">
-        <v>603.78725</v>
+        <v>603.7872459</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -10643,7 +10643,7 @@
         <v>52.15089</v>
       </c>
       <c r="H72">
-        <v>227.48203</v>
+        <v>227.4820344</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -10669,7 +10669,7 @@
         <v>36.82796</v>
       </c>
       <c r="H73">
-        <v>233.63179</v>
+        <v>233.1836582</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -10695,7 +10695,7 @@
         <v>149.18265</v>
       </c>
       <c r="H74">
-        <v>421.87835</v>
+        <v>421.8783485</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -10721,7 +10721,7 @@
         <v>220.53051</v>
       </c>
       <c r="H75">
-        <v>813.24195</v>
+        <v>813.2419474</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -10747,7 +10747,7 @@
         <v>21.14048</v>
       </c>
       <c r="H76">
-        <v>177.07849</v>
+        <v>177.0784862</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -10773,7 +10773,7 @@
         <v>13.80612</v>
       </c>
       <c r="H77">
-        <v>119.64491</v>
+        <v>119.6449094</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -10799,7 +10799,7 @@
         <v>74.58787</v>
       </c>
       <c r="H78">
-        <v>342.10618</v>
+        <v>272.3179654</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -10825,7 +10825,7 @@
         <v>13.73886</v>
       </c>
       <c r="H79">
-        <v>113.02761</v>
+        <v>148.027765</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -10851,7 +10851,7 @@
         <v>18.52304</v>
       </c>
       <c r="H80">
-        <v>134.55597</v>
+        <v>134.5559734</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -10877,7 +10877,7 @@
         <v>30.42078</v>
       </c>
       <c r="H81">
-        <v>299.01242</v>
+        <v>388.7986814</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -10903,7 +10903,7 @@
         <v>33.49526</v>
       </c>
       <c r="H82">
-        <v>297.50304</v>
+        <v>297.5030425</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -10929,7 +10929,7 @@
         <v>183.0357</v>
       </c>
       <c r="H83">
-        <v>298.59177</v>
+        <v>298.5917708</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -10955,7 +10955,7 @@
         <v>36.27607</v>
       </c>
       <c r="H84">
-        <v>191.57385</v>
+        <v>212.5593824</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -10981,7 +10981,7 @@
         <v>30.47681</v>
       </c>
       <c r="H85">
-        <v>155.9184</v>
+        <v>155.9184034</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -11007,7 +11007,7 @@
         <v>103.15899</v>
       </c>
       <c r="H86">
-        <v>283.31732</v>
+        <v>283.3173194</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -11033,7 +11033,7 @@
         <v>18.11248</v>
       </c>
       <c r="H87">
-        <v>292.19365</v>
+        <v>292.1936458</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -11059,7 +11059,7 @@
         <v>168.27787</v>
       </c>
       <c r="H88">
-        <v>318.43668</v>
+        <v>300.2805247</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -11085,7 +11085,7 @@
         <v>73.93901</v>
       </c>
       <c r="H89">
-        <v>305.05145</v>
+        <v>232.8827537</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -11111,7 +11111,7 @@
         <v>242.06617</v>
       </c>
       <c r="H90">
-        <v>537.78679</v>
+        <v>537.786787</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -11137,7 +11137,7 @@
         <v>92.67896</v>
       </c>
       <c r="H91">
-        <v>375.62383</v>
+        <v>295.5856477</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -11163,7 +11163,7 @@
         <v>72.8304</v>
       </c>
       <c r="H92">
-        <v>276.66514</v>
+        <v>276.6651369</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -11189,7 +11189,7 @@
         <v>73.58239</v>
       </c>
       <c r="H93">
-        <v>323.19684</v>
+        <v>323.1968401</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -11215,7 +11215,7 @@
         <v>45.22318</v>
       </c>
       <c r="H94">
-        <v>240.18121</v>
+        <v>240.1812116</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -11241,7 +11241,7 @@
         <v>22.51707</v>
       </c>
       <c r="H95">
-        <v>228.19806</v>
+        <v>239.0328526</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -11267,7 +11267,7 @@
         <v>321.89238</v>
       </c>
       <c r="H96">
-        <v>509.77842</v>
+        <v>509.7784232</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -11293,7 +11293,7 @@
         <v>65.17934</v>
       </c>
       <c r="H97">
-        <v>459.38</v>
+        <v>459.3799979</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -11319,7 +11319,7 @@
         <v>68.65169</v>
       </c>
       <c r="H98">
-        <v>260.52504</v>
+        <v>260.5250392</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -11345,7 +11345,7 @@
         <v>48.73481</v>
       </c>
       <c r="H99">
-        <v>282.5615</v>
+        <v>282.5614969</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -11371,7 +11371,7 @@
         <v>23.93325</v>
       </c>
       <c r="H100">
-        <v>114.77693</v>
+        <v>114.7769252</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -11397,7 +11397,7 @@
         <v>141.52248</v>
       </c>
       <c r="H101">
-        <v>361.77404</v>
+        <v>361.7740416</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -11423,7 +11423,7 @@
         <v>62.5185</v>
       </c>
       <c r="H102">
-        <v>239.86464</v>
+        <v>239.864642</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -11449,7 +11449,7 @@
         <v>357.454</v>
       </c>
       <c r="H103">
-        <v>768.65895</v>
+        <v>712.1015913</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -11475,7 +11475,7 @@
         <v>300.10818</v>
       </c>
       <c r="H104">
-        <v>698.71801</v>
+        <v>690.9327486</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -11501,7 +11501,7 @@
         <v>222.21164</v>
       </c>
       <c r="H105">
-        <v>464.12259</v>
+        <v>444.1421691</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -11527,7 +11527,7 @@
         <v>200.76839</v>
       </c>
       <c r="H106">
-        <v>326.38734</v>
+        <v>326.3873389</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -11553,7 +11553,7 @@
         <v>37.13341</v>
       </c>
       <c r="H107">
-        <v>201.81525</v>
+        <v>200.4692093</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -11579,7 +11579,7 @@
         <v>332.98078</v>
       </c>
       <c r="H108">
-        <v>637.72549</v>
+        <v>637.7254868</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -11605,7 +11605,7 @@
         <v>282.97144</v>
       </c>
       <c r="H109">
-        <v>375.01506</v>
+        <v>375.0150639</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -11631,7 +11631,7 @@
         <v>216.65818</v>
       </c>
       <c r="H110">
-        <v>572.02897</v>
+        <v>572.0289739</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -11657,7 +11657,7 @@
         <v>19.99393</v>
       </c>
       <c r="H111">
-        <v>102.35267</v>
+        <v>102.3526683</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -11683,7 +11683,7 @@
         <v>17.20903</v>
       </c>
       <c r="H112">
-        <v>208.63126</v>
+        <v>208.6312556</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -11709,7 +11709,7 @@
         <v>121.51284</v>
       </c>
       <c r="H113">
-        <v>312.06259</v>
+        <v>276.5165383</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -11735,7 +11735,7 @@
         <v>195.19885</v>
       </c>
       <c r="H114">
-        <v>434.76295</v>
+        <v>373.8775572</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -11761,7 +11761,7 @@
         <v>39.47085</v>
       </c>
       <c r="H115">
-        <v>230.85579</v>
+        <v>230.8557945</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -11787,7 +11787,7 @@
         <v>79.12128</v>
       </c>
       <c r="H116">
-        <v>587.79196</v>
+        <v>587.7919598</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -11813,7 +11813,7 @@
         <v>43.66015</v>
       </c>
       <c r="H117">
-        <v>255.96924</v>
+        <v>255.9692357</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -11839,7 +11839,7 @@
         <v>86.93098000000001</v>
       </c>
       <c r="H118">
-        <v>318.34681</v>
+        <v>279.4483568</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -11865,7 +11865,7 @@
         <v>50.45382</v>
       </c>
       <c r="H119">
-        <v>209.60959</v>
+        <v>209.6095871</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -11891,7 +11891,7 @@
         <v>202.72232</v>
       </c>
       <c r="H120">
-        <v>474.05294</v>
+        <v>474.0529393</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -11917,7 +11917,7 @@
         <v>316.75766</v>
       </c>
       <c r="H121">
-        <v>551.54174</v>
+        <v>551.5417425000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -11943,7 +11943,7 @@
         <v>359.73101</v>
       </c>
       <c r="H122">
-        <v>676.14514</v>
+        <v>676.1451415</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -11969,7 +11969,7 @@
         <v>339.12781</v>
       </c>
       <c r="H123">
-        <v>710.22725</v>
+        <v>710.2272484</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -11995,7 +11995,7 @@
         <v>48.47203</v>
       </c>
       <c r="H124">
-        <v>212.52884</v>
+        <v>212.5288433</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -12021,7 +12021,7 @@
         <v>60.8497</v>
       </c>
       <c r="H125">
-        <v>202.79113</v>
+        <v>146.4877157</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -12047,7 +12047,7 @@
         <v>78.69808999999999</v>
       </c>
       <c r="H126">
-        <v>309.99904</v>
+        <v>309.9990396</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -12073,7 +12073,7 @@
         <v>59.03008</v>
       </c>
       <c r="H127">
-        <v>225.12299</v>
+        <v>195.6182695</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -12099,7 +12099,7 @@
         <v>66.34034</v>
       </c>
       <c r="H128">
-        <v>277.56504</v>
+        <v>203.1049883</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -12125,7 +12125,7 @@
         <v>89.56367</v>
       </c>
       <c r="H129">
-        <v>245.35942</v>
+        <v>210.8203352</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -12151,7 +12151,7 @@
         <v>329.97471</v>
       </c>
       <c r="H130">
-        <v>673.21993</v>
+        <v>673.219932</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -12177,7 +12177,7 @@
         <v>100.9301</v>
       </c>
       <c r="H131">
-        <v>298.96648</v>
+        <v>298.9664782</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -12203,7 +12203,7 @@
         <v>39.43581</v>
       </c>
       <c r="H132">
-        <v>239.69573</v>
+        <v>213.1652207</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -12229,7 +12229,7 @@
         <v>317.35352</v>
       </c>
       <c r="H133">
-        <v>474.31888</v>
+        <v>474.3188829</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -12255,7 +12255,7 @@
         <v>253.21758</v>
       </c>
       <c r="H134">
-        <v>410.29848</v>
+        <v>410.298481</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -12281,7 +12281,7 @@
         <v>140.64651</v>
       </c>
       <c r="H135">
-        <v>291.79155</v>
+        <v>289.9292059</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -12307,7 +12307,7 @@
         <v>27.37949</v>
       </c>
       <c r="H136">
-        <v>298.02338</v>
+        <v>298.0233833</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -12333,7 +12333,7 @@
         <v>85.20841</v>
       </c>
       <c r="H137">
-        <v>292.8393</v>
+        <v>237.8111069</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -12359,7 +12359,7 @@
         <v>15.51592</v>
       </c>
       <c r="H138">
-        <v>164.45724</v>
+        <v>223.8995639</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -12385,7 +12385,7 @@
         <v>29.83619</v>
       </c>
       <c r="H139">
-        <v>307.57338</v>
+        <v>307.5733777</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -12411,7 +12411,7 @@
         <v>123.53978</v>
       </c>
       <c r="H140">
-        <v>446.99671</v>
+        <v>446.9967085</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -12437,7 +12437,7 @@
         <v>68.23000999999999</v>
       </c>
       <c r="H141">
-        <v>353.51545</v>
+        <v>353.5154541</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -12463,7 +12463,7 @@
         <v>274.97842</v>
       </c>
       <c r="H142">
-        <v>576.54922</v>
+        <v>576.5492240999999</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -12489,7 +12489,7 @@
         <v>307.10148</v>
       </c>
       <c r="H143">
-        <v>664.97315</v>
+        <v>664.9731548</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -12515,7 +12515,7 @@
         <v>304.1839</v>
       </c>
       <c r="H144">
-        <v>550.03831</v>
+        <v>550.0383098999999</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -12541,7 +12541,7 @@
         <v>293.66664</v>
       </c>
       <c r="H145">
-        <v>558.40876</v>
+        <v>558.4087552</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -12567,7 +12567,7 @@
         <v>253.81658</v>
       </c>
       <c r="H146">
-        <v>501.85973</v>
+        <v>501.8597278</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -12593,7 +12593,7 @@
         <v>93.07826</v>
       </c>
       <c r="H147">
-        <v>299.3993</v>
+        <v>230.4097692</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -12619,7 +12619,7 @@
         <v>111.29802</v>
       </c>
       <c r="H148">
-        <v>272.4805</v>
+        <v>272.4805043</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -12645,7 +12645,7 @@
         <v>90.61344</v>
       </c>
       <c r="H149">
-        <v>299.06762</v>
+        <v>232.2165712</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -12671,7 +12671,7 @@
         <v>455.37615</v>
       </c>
       <c r="H150">
-        <v>463.9819</v>
+        <v>463.9818976</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -12697,7 +12697,7 @@
         <v>22.48164</v>
       </c>
       <c r="H151">
-        <v>160.29395</v>
+        <v>209.2073047</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -12723,7 +12723,7 @@
         <v>229.39389</v>
       </c>
       <c r="H152">
-        <v>571.26712</v>
+        <v>571.2671179</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -12749,7 +12749,7 @@
         <v>180.84678</v>
       </c>
       <c r="H153">
-        <v>359.50687</v>
+        <v>359.5068739</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -12775,7 +12775,7 @@
         <v>96.11188</v>
       </c>
       <c r="H154">
-        <v>297.67527</v>
+        <v>226.9051111</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -12801,7 +12801,7 @@
         <v>129.96675</v>
       </c>
       <c r="H155">
-        <v>336.60487</v>
+        <v>336.6048741</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -12827,7 +12827,7 @@
         <v>28.45004</v>
       </c>
       <c r="H156">
-        <v>183.51946</v>
+        <v>202.5506742</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -12853,7 +12853,7 @@
         <v>43.82167</v>
       </c>
       <c r="H157">
-        <v>216.43024</v>
+        <v>166.0024971</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -12879,7 +12879,7 @@
         <v>36.63331</v>
       </c>
       <c r="H158">
-        <v>172.69715</v>
+        <v>172.6971533</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -12905,7 +12905,7 @@
         <v>63.05236</v>
       </c>
       <c r="H159">
-        <v>258.73014</v>
+        <v>275.8074481</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -12931,7 +12931,7 @@
         <v>361.94296</v>
       </c>
       <c r="H160">
-        <v>497.33892</v>
+        <v>497.3389204</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -12957,7 +12957,7 @@
         <v>88.80925999999999</v>
       </c>
       <c r="H161">
-        <v>252.90674</v>
+        <v>236.0040026</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -12983,7 +12983,7 @@
         <v>71.97331</v>
       </c>
       <c r="H162">
-        <v>202.45541</v>
+        <v>164.4852342</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -13009,7 +13009,7 @@
         <v>60.45917</v>
       </c>
       <c r="H163">
-        <v>364.22498</v>
+        <v>364.2249839</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -13035,7 +13035,7 @@
         <v>91.52524</v>
       </c>
       <c r="H164">
-        <v>219.62315</v>
+        <v>219.6231452</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -13061,7 +13061,7 @@
         <v>267.12837</v>
       </c>
       <c r="H165">
-        <v>603.07413</v>
+        <v>603.0741258</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -13087,7 +13087,7 @@
         <v>289.94465</v>
       </c>
       <c r="H166">
-        <v>551.24195</v>
+        <v>551.241951</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -13113,7 +13113,7 @@
         <v>298.50173</v>
       </c>
       <c r="H167">
-        <v>565.89521</v>
+        <v>565.8952141</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -13139,7 +13139,7 @@
         <v>274.86387</v>
       </c>
       <c r="H168">
-        <v>550.14405</v>
+        <v>550.1440545</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -13165,7 +13165,7 @@
         <v>252.18623</v>
       </c>
       <c r="H169">
-        <v>488.05139</v>
+        <v>488.051392</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -13191,7 +13191,7 @@
         <v>204.64248</v>
       </c>
       <c r="H170">
-        <v>523.26924</v>
+        <v>523.2692386</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -13217,7 +13217,7 @@
         <v>277.33878</v>
       </c>
       <c r="H171">
-        <v>490.783</v>
+        <v>490.7830039</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -13243,7 +13243,7 @@
         <v>268.73434</v>
       </c>
       <c r="H172">
-        <v>552.63984</v>
+        <v>552.6398364</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -13269,7 +13269,7 @@
         <v>33.70572</v>
       </c>
       <c r="H173">
-        <v>186.53904</v>
+        <v>153.6427395</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -13295,7 +13295,7 @@
         <v>33.66</v>
       </c>
       <c r="H174">
-        <v>180.11683</v>
+        <v>180.1168331</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -13321,7 +13321,7 @@
         <v>55.3513</v>
       </c>
       <c r="H175">
-        <v>273.7849</v>
+        <v>273.7848955</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -13347,7 +13347,7 @@
         <v>12.33358</v>
       </c>
       <c r="H176">
-        <v>89.01409</v>
+        <v>89.01409040999999</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -13373,7 +13373,7 @@
         <v>28.54242</v>
       </c>
       <c r="H177">
-        <v>204.43619</v>
+        <v>172.8573326</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -13399,7 +13399,7 @@
         <v>28.21346</v>
       </c>
       <c r="H178">
-        <v>224.83416</v>
+        <v>196.7290703</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -13425,7 +13425,7 @@
         <v>33.25383</v>
       </c>
       <c r="H179">
-        <v>255.11021</v>
+        <v>250.8794101</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -13451,7 +13451,7 @@
         <v>24.21172</v>
       </c>
       <c r="H180">
-        <v>157.47917</v>
+        <v>182.9013068</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -13477,7 +13477,7 @@
         <v>52.58964</v>
       </c>
       <c r="H181">
-        <v>217.72607</v>
+        <v>217.7260718</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -13503,7 +13503,7 @@
         <v>46.77689</v>
       </c>
       <c r="H182">
-        <v>224.4603</v>
+        <v>224.4603045</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -13529,7 +13529,7 @@
         <v>15.72569</v>
       </c>
       <c r="H183">
-        <v>118.29788</v>
+        <v>203.6842851</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -13555,7 +13555,7 @@
         <v>15.01902</v>
       </c>
       <c r="H184">
-        <v>107.76432</v>
+        <v>107.7643221</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -13581,7 +13581,7 @@
         <v>51.85</v>
       </c>
       <c r="H185">
-        <v>324.68605</v>
+        <v>250.6120711</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -13607,7 +13607,7 @@
         <v>20.35192</v>
       </c>
       <c r="H186">
-        <v>281.10452</v>
+        <v>281.1045249</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -13633,7 +13633,7 @@
         <v>105.7977</v>
       </c>
       <c r="H187">
-        <v>276.33241</v>
+        <v>276.3324141</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -13659,7 +13659,7 @@
         <v>15.81087</v>
       </c>
       <c r="H188">
-        <v>111.43024</v>
+        <v>111.4302393</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -13685,7 +13685,7 @@
         <v>13.3231</v>
       </c>
       <c r="H189">
-        <v>96.83595</v>
+        <v>96.8359538</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -13711,7 +13711,7 @@
         <v>100.89003</v>
       </c>
       <c r="H190">
-        <v>307.06161</v>
+        <v>307.0616119</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -13737,7 +13737,7 @@
         <v>95.73514</v>
       </c>
       <c r="H191">
-        <v>290.84547</v>
+        <v>290.8454692</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -13763,7 +13763,7 @@
         <v>182.7917</v>
       </c>
       <c r="H192">
-        <v>551.51275</v>
+        <v>551.5127526</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -13789,7 +13789,7 @@
         <v>67.48063999999999</v>
       </c>
       <c r="H193">
-        <v>452.28706</v>
+        <v>452.2870649</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -13815,7 +13815,7 @@
         <v>92.52325999999999</v>
       </c>
       <c r="H194">
-        <v>302.33133</v>
+        <v>302.3313324</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -13841,7 +13841,7 @@
         <v>11.67317</v>
       </c>
       <c r="H195">
-        <v>102.81226</v>
+        <v>102.8122571</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -13867,7 +13867,7 @@
         <v>17.42749</v>
       </c>
       <c r="H196">
-        <v>129.54295</v>
+        <v>129.5429547</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -13893,7 +13893,7 @@
         <v>15.29234</v>
       </c>
       <c r="H197">
-        <v>110.12838</v>
+        <v>156.0704821</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -13919,7 +13919,7 @@
         <v>18.252</v>
       </c>
       <c r="H198">
-        <v>113.33551</v>
+        <v>113.3355148</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -13945,7 +13945,7 @@
         <v>17.10586</v>
       </c>
       <c r="H199">
-        <v>103.06129</v>
+        <v>103.0612857</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -13971,7 +13971,7 @@
         <v>21.44243</v>
       </c>
       <c r="H200">
-        <v>185.03653</v>
+        <v>185.0365332</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -13997,7 +13997,7 @@
         <v>19.23063</v>
       </c>
       <c r="H201">
-        <v>144.84712</v>
+        <v>144.8471157</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -14023,7 +14023,7 @@
         <v>21.62743</v>
       </c>
       <c r="H202">
-        <v>128.49686</v>
+        <v>128.4968632</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -14049,7 +14049,7 @@
         <v>23.68691</v>
       </c>
       <c r="H203">
-        <v>237.10039</v>
+        <v>269.5081157</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -14075,7 +14075,7 @@
         <v>91.79922999999999</v>
       </c>
       <c r="H204">
-        <v>427.74501</v>
+        <v>427.7450063</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -14101,7 +14101,7 @@
         <v>126.1842</v>
       </c>
       <c r="H205">
-        <v>398.20044</v>
+        <v>398.2004371</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -14127,7 +14127,7 @@
         <v>54.93035</v>
       </c>
       <c r="H206">
-        <v>199.7238</v>
+        <v>199.7238033</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -14153,7 +14153,7 @@
         <v>46.03402</v>
       </c>
       <c r="H207">
-        <v>227.23069</v>
+        <v>219.2198187</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -14179,7 +14179,7 @@
         <v>37.29564</v>
       </c>
       <c r="H208">
-        <v>184.59379</v>
+        <v>187.6692153</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -14205,7 +14205,7 @@
         <v>11.57184</v>
       </c>
       <c r="H209">
-        <v>164.37934</v>
+        <v>164.3793426</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -14231,7 +14231,7 @@
         <v>50.39453</v>
       </c>
       <c r="H210">
-        <v>189.94522</v>
+        <v>189.945218</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -14257,7 +14257,7 @@
         <v>35.08564</v>
       </c>
       <c r="H211">
-        <v>164.43768</v>
+        <v>164.4376844</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -14283,7 +14283,7 @@
         <v>8.99056</v>
       </c>
       <c r="H212">
-        <v>129.21628</v>
+        <v>129.2162806</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -14309,7 +14309,7 @@
         <v>13.09192</v>
       </c>
       <c r="H213">
-        <v>123.66303</v>
+        <v>123.663033</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -14335,7 +14335,7 @@
         <v>30.47342</v>
       </c>
       <c r="H214">
-        <v>196.03281</v>
+        <v>196.0328127</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -14361,7 +14361,7 @@
         <v>21.71097</v>
       </c>
       <c r="H215">
-        <v>161.02724</v>
+        <v>161.0272353</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -14387,7 +14387,7 @@
         <v>40.60014</v>
       </c>
       <c r="H216">
-        <v>317.71402</v>
+        <v>245.5445291</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -14413,7 +14413,7 @@
         <v>52.3387</v>
       </c>
       <c r="H217">
-        <v>273.31091</v>
+        <v>366.147547</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -14439,7 +14439,7 @@
         <v>39.65203</v>
       </c>
       <c r="H218">
-        <v>333.90264</v>
+        <v>333.9026388</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -14465,7 +14465,7 @@
         <v>9.85722</v>
       </c>
       <c r="H219">
-        <v>165.28509</v>
+        <v>165.2850931</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -14491,7 +14491,7 @@
         <v>56.51014</v>
       </c>
       <c r="H220">
-        <v>317.25327</v>
+        <v>317.2532746</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -14517,7 +14517,7 @@
         <v>48.47089</v>
       </c>
       <c r="H221">
-        <v>235.68471</v>
+        <v>235.6847063</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -14543,7 +14543,7 @@
         <v>55.50289</v>
       </c>
       <c r="H222">
-        <v>276.19058</v>
+        <v>276.1905805</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -14569,7 +14569,7 @@
         <v>47.99592</v>
       </c>
       <c r="H223">
-        <v>215.84629</v>
+        <v>246.10934</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -14595,7 +14595,7 @@
         <v>60.08604</v>
       </c>
       <c r="H224">
-        <v>274.28184</v>
+        <v>229.5180838</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -14621,7 +14621,7 @@
         <v>55.17582</v>
       </c>
       <c r="H225">
-        <v>277.05766</v>
+        <v>277.0576644</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -14647,7 +14647,7 @@
         <v>47.38406</v>
       </c>
       <c r="H226">
-        <v>215.03661</v>
+        <v>196.1749754</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -14673,7 +14673,7 @@
         <v>35.84127</v>
       </c>
       <c r="H227">
-        <v>177.2289</v>
+        <v>150.8782371</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -14699,7 +14699,7 @@
         <v>54.86138</v>
       </c>
       <c r="H228">
-        <v>249.29899</v>
+        <v>249.2989852</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -14725,7 +14725,7 @@
         <v>46.58784</v>
       </c>
       <c r="H229">
-        <v>198.52375</v>
+        <v>198.5237469</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -14751,7 +14751,7 @@
         <v>34.8225</v>
       </c>
       <c r="H230">
-        <v>164.00858</v>
+        <v>164.008576</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -14777,7 +14777,7 @@
         <v>27.97421</v>
       </c>
       <c r="H231">
-        <v>222.61132</v>
+        <v>222.611316</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -14803,7 +14803,7 @@
         <v>39.82754</v>
       </c>
       <c r="H232">
-        <v>294.91366</v>
+        <v>386.6282512</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -14829,7 +14829,7 @@
         <v>56.87046</v>
       </c>
       <c r="H233">
-        <v>302.25083</v>
+        <v>302.2508291</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -14855,7 +14855,7 @@
         <v>48.15109</v>
       </c>
       <c r="H234">
-        <v>226.44054</v>
+        <v>226.4405419</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -14881,7 +14881,7 @@
         <v>26.73174</v>
       </c>
       <c r="H235">
-        <v>199.70755</v>
+        <v>199.7075527</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -14907,7 +14907,7 @@
         <v>155.16155</v>
       </c>
       <c r="H236">
-        <v>406.17976</v>
+        <v>406.1797558</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -14933,7 +14933,7 @@
         <v>33.72743</v>
       </c>
       <c r="H237">
-        <v>151.52527</v>
+        <v>139.0122235</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -14959,7 +14959,7 @@
         <v>70.72682</v>
       </c>
       <c r="H238">
-        <v>333.24699</v>
+        <v>333.2469946</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -14985,7 +14985,7 @@
         <v>59.50326</v>
       </c>
       <c r="H239">
-        <v>249.82918</v>
+        <v>249.829181</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -15011,7 +15011,7 @@
         <v>43.5864</v>
       </c>
       <c r="H240">
-        <v>200.83947</v>
+        <v>161.7252148</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -15037,7 +15037,7 @@
         <v>163.75499</v>
       </c>
       <c r="H241">
-        <v>387.9049</v>
+        <v>387.9049042</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -15063,7 +15063,7 @@
         <v>118.98084</v>
       </c>
       <c r="H242">
-        <v>364.4546</v>
+        <v>364.454597</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -15089,7 +15089,7 @@
         <v>135.6414</v>
       </c>
       <c r="H243">
-        <v>472.64822</v>
+        <v>472.6482189</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -15115,7 +15115,7 @@
         <v>32.16949</v>
       </c>
       <c r="H244">
-        <v>464.62001</v>
+        <v>464.620008</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -15141,7 +15141,7 @@
         <v>105.69975</v>
       </c>
       <c r="H245">
-        <v>423.26107</v>
+        <v>423.2610676</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -15167,7 +15167,7 @@
         <v>44.05286</v>
       </c>
       <c r="H246">
-        <v>232.72207</v>
+        <v>232.7220689</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -15193,7 +15193,7 @@
         <v>263.64006</v>
       </c>
       <c r="H247">
-        <v>529.8549400000001</v>
+        <v>529.8549399</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -15219,7 +15219,7 @@
         <v>48.92606</v>
       </c>
       <c r="H248">
-        <v>255.03685</v>
+        <v>261.5453867</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -15245,7 +15245,7 @@
         <v>44.97646</v>
       </c>
       <c r="H249">
-        <v>203.19487</v>
+        <v>203.1948691</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -15271,7 +15271,7 @@
         <v>28.30352</v>
       </c>
       <c r="H250">
-        <v>267.26648</v>
+        <v>267.2664814</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -15297,7 +15297,7 @@
         <v>59.33461</v>
       </c>
       <c r="H251">
-        <v>236.10431</v>
+        <v>176.9139229</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -15323,7 +15323,7 @@
         <v>74.18714</v>
       </c>
       <c r="H252">
-        <v>280.20133</v>
+        <v>280.2013316</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -15349,7 +15349,7 @@
         <v>59.64434</v>
       </c>
       <c r="H253">
-        <v>221.41902</v>
+        <v>181.8270742</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -15375,7 +15375,7 @@
         <v>53.24687</v>
       </c>
       <c r="H254">
-        <v>204.39043</v>
+        <v>204.3904264</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -15401,7 +15401,7 @@
         <v>59.3965</v>
       </c>
       <c r="H255">
-        <v>240.35028</v>
+        <v>240.3502756</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -15427,7 +15427,7 @@
         <v>68.69833</v>
       </c>
       <c r="H256">
-        <v>291.95071</v>
+        <v>291.9507139</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -15453,7 +15453,7 @@
         <v>51.66569</v>
       </c>
       <c r="H257">
-        <v>264.38862</v>
+        <v>264.3886202</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -15479,7 +15479,7 @@
         <v>35.64164</v>
       </c>
       <c r="H258">
-        <v>222.7744</v>
+        <v>222.7744027</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -15505,7 +15505,7 @@
         <v>63.96519</v>
       </c>
       <c r="H259">
-        <v>287.16462</v>
+        <v>287.1646181</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -15531,7 +15531,7 @@
         <v>51.47509</v>
       </c>
       <c r="H260">
-        <v>220.86699</v>
+        <v>220.8669872</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -15557,7 +15557,7 @@
         <v>155.48588</v>
       </c>
       <c r="H261">
-        <v>564.98896</v>
+        <v>564.9889595</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -15583,7 +15583,7 @@
         <v>96.74764999999999</v>
       </c>
       <c r="H262">
-        <v>368.73075</v>
+        <v>295.9427481</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -15609,7 +15609,7 @@
         <v>87.03843999999999</v>
       </c>
       <c r="H263">
-        <v>349.22335</v>
+        <v>349.2233532</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -15635,7 +15635,7 @@
         <v>58.49674</v>
       </c>
       <c r="H264">
-        <v>286.69101</v>
+        <v>286.6910116</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -15661,7 +15661,7 @@
         <v>50.82527</v>
       </c>
       <c r="H265">
-        <v>226.47379</v>
+        <v>226.4737882</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -15687,7 +15687,7 @@
         <v>93.20948</v>
       </c>
       <c r="H266">
-        <v>404.01879</v>
+        <v>316.77803</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -15713,7 +15713,7 @@
         <v>74.31975</v>
       </c>
       <c r="H267">
-        <v>293.31334</v>
+        <v>228.8905584</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -15739,7 +15739,7 @@
         <v>90.47462</v>
       </c>
       <c r="H268">
-        <v>329.77461</v>
+        <v>257.4544967</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -15765,7 +15765,7 @@
         <v>101.097</v>
       </c>
       <c r="H269">
-        <v>380.4224</v>
+        <v>372.3517536</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -15791,7 +15791,7 @@
         <v>75.00511</v>
       </c>
       <c r="H270">
-        <v>280.58239</v>
+        <v>280.5823939</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -15817,7 +15817,7 @@
         <v>154.4739</v>
       </c>
       <c r="H271">
-        <v>553.26859</v>
+        <v>553.2685936</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -15843,7 +15843,7 @@
         <v>59.895</v>
       </c>
       <c r="H272">
-        <v>265.09678</v>
+        <v>265.0967759</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -15869,7 +15869,7 @@
         <v>49.80614</v>
       </c>
       <c r="H273">
-        <v>210.37954</v>
+        <v>210.3795373</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -15895,7 +15895,7 @@
         <v>92.58924</v>
       </c>
       <c r="H274">
-        <v>360.16392</v>
+        <v>360.1639202</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -15921,7 +15921,7 @@
         <v>73.48480000000001</v>
       </c>
       <c r="H275">
-        <v>272.02371</v>
+        <v>272.0237089</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -15947,7 +15947,7 @@
         <v>44.26798</v>
       </c>
       <c r="H276">
-        <v>212.61738</v>
+        <v>212.6173841</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -15973,7 +15973,7 @@
         <v>39.48865</v>
       </c>
       <c r="H277">
-        <v>178.71664</v>
+        <v>178.7166417</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -15999,7 +15999,7 @@
         <v>68.98913</v>
       </c>
       <c r="H278">
-        <v>283.21003</v>
+        <v>283.2100293</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -16025,7 +16025,7 @@
         <v>56.45428</v>
       </c>
       <c r="H279">
-        <v>224.37075</v>
+        <v>224.3707502</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -16051,7 +16051,7 @@
         <v>89.8635</v>
       </c>
       <c r="H280">
-        <v>472.86082</v>
+        <v>472.8608189</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -16077,7 +16077,7 @@
         <v>48.26025</v>
       </c>
       <c r="H281">
-        <v>184.73668</v>
+        <v>184.7366827</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -16103,7 +16103,7 @@
         <v>120.66537</v>
       </c>
       <c r="H282">
-        <v>419.94019</v>
+        <v>419.9401893</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -16129,7 +16129,7 @@
         <v>134.03637</v>
       </c>
       <c r="H283">
-        <v>495.54295</v>
+        <v>495.5429521</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -16155,7 +16155,7 @@
         <v>97.95184999999999</v>
       </c>
       <c r="H284">
-        <v>346.20459</v>
+        <v>346.2045924</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -16181,7 +16181,7 @@
         <v>201.28221</v>
       </c>
       <c r="H285">
-        <v>291.18986</v>
+        <v>230.7801236</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -16207,7 +16207,7 @@
         <v>82.40481</v>
       </c>
       <c r="H286">
-        <v>268.12037</v>
+        <v>188.4549495</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -16233,7 +16233,7 @@
         <v>164.36797</v>
       </c>
       <c r="H287">
-        <v>254.2774</v>
+        <v>207.3923137</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -16259,7 +16259,7 @@
         <v>159.52817</v>
       </c>
       <c r="H288">
-        <v>331.66441</v>
+        <v>331.6644081</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -16285,7 +16285,7 @@
         <v>184.16661</v>
       </c>
       <c r="H289">
-        <v>272.76541</v>
+        <v>272.7654055</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -16311,7 +16311,7 @@
         <v>124.97856</v>
       </c>
       <c r="H290">
-        <v>268.43813</v>
+        <v>268.4381347</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -16337,7 +16337,7 @@
         <v>144.59021</v>
       </c>
       <c r="H291">
-        <v>307.05797</v>
+        <v>307.0579701</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -16363,7 +16363,7 @@
         <v>157.05079</v>
       </c>
       <c r="H292">
-        <v>247.81778</v>
+        <v>247.8177768</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -16389,7 +16389,7 @@
         <v>50.07241</v>
       </c>
       <c r="H293">
-        <v>260.64581</v>
+        <v>260.645812</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -16415,7 +16415,7 @@
         <v>100.40077</v>
       </c>
       <c r="H294">
-        <v>383.99097</v>
+        <v>383.9909726</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -16441,7 +16441,7 @@
         <v>151.73635</v>
       </c>
       <c r="H295">
-        <v>337.87919</v>
+        <v>337.8791902</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -16467,7 +16467,7 @@
         <v>199.81238</v>
       </c>
       <c r="H296">
-        <v>292.48421</v>
+        <v>292.4842145</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -16493,7 +16493,7 @@
         <v>116.55642</v>
       </c>
       <c r="H297">
-        <v>273.24946</v>
+        <v>273.2494551</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -16519,7 +16519,7 @@
         <v>129.71358</v>
       </c>
       <c r="H298">
-        <v>273.83869</v>
+        <v>273.8386908</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -16545,7 +16545,7 @@
         <v>147.04704</v>
       </c>
       <c r="H299">
-        <v>318.96035</v>
+        <v>318.9603537</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -16571,7 +16571,7 @@
         <v>196.23206</v>
       </c>
       <c r="H300">
-        <v>282.76774</v>
+        <v>282.7677379</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -16597,7 +16597,7 @@
         <v>124.72235</v>
       </c>
       <c r="H301">
-        <v>285.7052</v>
+        <v>285.7052027</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -16623,7 +16623,7 @@
         <v>23.45594</v>
       </c>
       <c r="H302">
-        <v>136.8057</v>
+        <v>136.8057022</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -16649,7 +16649,7 @@
         <v>156.21619</v>
       </c>
       <c r="H303">
-        <v>397.13457</v>
+        <v>397.134574</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -16675,7 +16675,7 @@
         <v>26.77878</v>
       </c>
       <c r="H304">
-        <v>186.47057</v>
+        <v>154.9334555</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -16701,7 +16701,7 @@
         <v>42.92619</v>
       </c>
       <c r="H305">
-        <v>261.64126</v>
+        <v>340.7726213</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -16727,7 +16727,7 @@
         <v>33.04714</v>
       </c>
       <c r="H306">
-        <v>188.62838</v>
+        <v>188.6283805</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -16753,7 +16753,7 @@
         <v>202.39328</v>
       </c>
       <c r="H307">
-        <v>384.70006</v>
+        <v>384.7000601</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -16779,7 +16779,7 @@
         <v>180.79844</v>
       </c>
       <c r="H308">
-        <v>342.10984</v>
+        <v>342.1098437</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -16805,7 +16805,7 @@
         <v>227.89542</v>
       </c>
       <c r="H309">
-        <v>443.34616</v>
+        <v>443.3461559</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -16831,7 +16831,7 @@
         <v>128.74424</v>
       </c>
       <c r="H310">
-        <v>312.35296</v>
+        <v>312.3529621</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -16857,7 +16857,7 @@
         <v>22.81615</v>
       </c>
       <c r="H311">
-        <v>210.96621</v>
+        <v>210.9662131</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -16883,7 +16883,7 @@
         <v>34.08914</v>
       </c>
       <c r="H312">
-        <v>186.86918</v>
+        <v>186.8691799</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -16909,7 +16909,7 @@
         <v>38.05072</v>
       </c>
       <c r="H313">
-        <v>265.66754</v>
+        <v>265.6675377</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -16935,7 +16935,7 @@
         <v>124.48238</v>
       </c>
       <c r="H314">
-        <v>504.61566</v>
+        <v>504.6156564</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -16961,7 +16961,7 @@
         <v>58.32667</v>
       </c>
       <c r="H315">
-        <v>443.47713</v>
+        <v>443.4771311</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -16987,7 +16987,7 @@
         <v>66.57395</v>
       </c>
       <c r="H316">
-        <v>344.19374</v>
+        <v>285.8490836</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -17013,7 +17013,7 @@
         <v>31.2283</v>
       </c>
       <c r="H317">
-        <v>230.53494</v>
+        <v>230.5349365</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -17039,7 +17039,7 @@
         <v>58.84173</v>
       </c>
       <c r="H318">
-        <v>244.42692</v>
+        <v>244.4269219</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -17065,7 +17065,7 @@
         <v>61.10554</v>
       </c>
       <c r="H319">
-        <v>172.40174</v>
+        <v>172.4017431</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -17091,7 +17091,7 @@
         <v>107.37916</v>
       </c>
       <c r="H320">
-        <v>257.30962</v>
+        <v>257.3096198</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -17117,7 +17117,7 @@
         <v>118.9725</v>
       </c>
       <c r="H321">
-        <v>260.38951</v>
+        <v>260.3895069</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -17143,7 +17143,7 @@
         <v>191.8612</v>
       </c>
       <c r="H322">
-        <v>452.87922</v>
+        <v>452.879216</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -17169,7 +17169,7 @@
         <v>169.05559</v>
       </c>
       <c r="H323">
-        <v>387.5831</v>
+        <v>387.5831022</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -17195,7 +17195,7 @@
         <v>127.91257</v>
       </c>
       <c r="H324">
-        <v>372.29321</v>
+        <v>372.2932077</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -17221,7 +17221,7 @@
         <v>212.91614</v>
       </c>
       <c r="H325">
-        <v>540.6369999999999</v>
+        <v>540.6370034</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -17247,7 +17247,7 @@
         <v>64.14521999999999</v>
       </c>
       <c r="H326">
-        <v>265.34076</v>
+        <v>265.3407623</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -17273,7 +17273,7 @@
         <v>93.77819</v>
       </c>
       <c r="H327">
-        <v>233.27835</v>
+        <v>302.5377874</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -17299,7 +17299,7 @@
         <v>87.30234</v>
       </c>
       <c r="H328">
-        <v>763.99275</v>
+        <v>763.9927455</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -17325,7 +17325,7 @@
         <v>66.21071999999999</v>
       </c>
       <c r="H329">
-        <v>470.14188</v>
+        <v>470.1418831</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -17351,7 +17351,7 @@
         <v>87.26609999999999</v>
       </c>
       <c r="H330">
-        <v>341.8243</v>
+        <v>341.8243009</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -17377,7 +17377,7 @@
         <v>139.10647</v>
       </c>
       <c r="H331">
-        <v>396.2153</v>
+        <v>396.2152971</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -17403,7 +17403,7 @@
         <v>121.49037</v>
       </c>
       <c r="H332">
-        <v>369.94701</v>
+        <v>369.9470097</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -17429,7 +17429,7 @@
         <v>94.2501</v>
       </c>
       <c r="H333">
-        <v>318.50488</v>
+        <v>318.5048773</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -17455,7 +17455,7 @@
         <v>92.1087</v>
       </c>
       <c r="H334">
-        <v>306.60011</v>
+        <v>274.3739015</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -17481,7 +17481,7 @@
         <v>125.11553</v>
       </c>
       <c r="H335">
-        <v>274.98673</v>
+        <v>274.9867295</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -17507,7 +17507,7 @@
         <v>104.06312</v>
       </c>
       <c r="H336">
-        <v>300.64113</v>
+        <v>300.6411338</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -17533,7 +17533,7 @@
         <v>123.54894</v>
       </c>
       <c r="H337">
-        <v>330.86659</v>
+        <v>330.8665885</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -17559,7 +17559,7 @@
         <v>73.97405999999999</v>
       </c>
       <c r="H338">
-        <v>284.81346</v>
+        <v>201.2015319</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -17585,7 +17585,7 @@
         <v>188.10089</v>
       </c>
       <c r="H339">
-        <v>537.4346</v>
+        <v>537.4345954</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -17611,7 +17611,7 @@
         <v>185.73282</v>
       </c>
       <c r="H340">
-        <v>541.4598</v>
+        <v>541.4598048</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -17637,7 +17637,7 @@
         <v>179.34199</v>
       </c>
       <c r="H341">
-        <v>516.55923</v>
+        <v>441.8946577</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -17663,7 +17663,7 @@
         <v>123.17699</v>
       </c>
       <c r="H342">
-        <v>357.83129</v>
+        <v>357.8312911</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -17689,7 +17689,7 @@
         <v>187.8568</v>
       </c>
       <c r="H343">
-        <v>462.01944</v>
+        <v>462.0194373</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -17715,7 +17715,7 @@
         <v>233.45107</v>
       </c>
       <c r="H344">
-        <v>487.0872</v>
+        <v>487.0871996</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -17741,7 +17741,7 @@
         <v>219.49578</v>
       </c>
       <c r="H345">
-        <v>480.00261</v>
+        <v>480.002606</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -17767,7 +17767,7 @@
         <v>180.56212</v>
       </c>
       <c r="H346">
-        <v>422.6463</v>
+        <v>422.6462958</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -17793,7 +17793,7 @@
         <v>77.28128</v>
       </c>
       <c r="H347">
-        <v>270.90254</v>
+        <v>270.9025376</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -17819,7 +17819,7 @@
         <v>85.21693</v>
       </c>
       <c r="H348">
-        <v>312.23209</v>
+        <v>312.2320868</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -17845,7 +17845,7 @@
         <v>25.74365</v>
       </c>
       <c r="H349">
-        <v>211.91</v>
+        <v>211.9100002</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -17871,7 +17871,7 @@
         <v>212.51329</v>
       </c>
       <c r="H350">
-        <v>438.76939</v>
+        <v>438.7693872</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -17897,7 +17897,7 @@
         <v>250.05763</v>
       </c>
       <c r="H351">
-        <v>436.11617</v>
+        <v>436.1161675</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -17923,7 +17923,7 @@
         <v>248.24874</v>
       </c>
       <c r="H352">
-        <v>438.27176</v>
+        <v>438.2717648</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -17949,7 +17949,7 @@
         <v>182.1216</v>
       </c>
       <c r="H353">
-        <v>425.58602</v>
+        <v>425.5860174</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -17975,7 +17975,7 @@
         <v>131.8304</v>
       </c>
       <c r="H354">
-        <v>320.35543</v>
+        <v>320.3554263</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -18001,7 +18001,7 @@
         <v>183.27116</v>
       </c>
       <c r="H355">
-        <v>379.69551</v>
+        <v>379.695506</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -18027,7 +18027,7 @@
         <v>104.14199</v>
       </c>
       <c r="H356">
-        <v>296.21452</v>
+        <v>296.2145206</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -18053,7 +18053,7 @@
         <v>211.46436</v>
       </c>
       <c r="H357">
-        <v>439.35696</v>
+        <v>439.3569588</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -18079,7 +18079,7 @@
         <v>248.33708</v>
       </c>
       <c r="H358">
-        <v>436.27241</v>
+        <v>436.2724143</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -18105,7 +18105,7 @@
         <v>78.18729999999999</v>
       </c>
       <c r="H359">
-        <v>346.55584</v>
+        <v>346.5558354</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -18131,7 +18131,7 @@
         <v>34.06826</v>
       </c>
       <c r="H360">
-        <v>194.19807</v>
+        <v>194.1980677</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -18157,7 +18157,7 @@
         <v>82.11839999999999</v>
       </c>
       <c r="H361">
-        <v>310.87743</v>
+        <v>310.8774347</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -18183,7 +18183,7 @@
         <v>20.44685</v>
       </c>
       <c r="H362">
-        <v>230.33084</v>
+        <v>230.3308432</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -18209,7 +18209,7 @@
         <v>41.6077</v>
       </c>
       <c r="H363">
-        <v>432.09486</v>
+        <v>432.0948579</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -18235,7 +18235,7 @@
         <v>98.41231999999999</v>
       </c>
       <c r="H364">
-        <v>393.77101</v>
+        <v>393.7710138</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -18261,7 +18261,7 @@
         <v>116.8014</v>
       </c>
       <c r="H365">
-        <v>432.38985</v>
+        <v>432.3898492</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -18287,7 +18287,7 @@
         <v>71.19188</v>
       </c>
       <c r="H366">
-        <v>410.27846</v>
+        <v>410.2784567</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -18313,7 +18313,7 @@
         <v>189.30662</v>
       </c>
       <c r="H367">
-        <v>442.12728</v>
+        <v>442.127276</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -18339,7 +18339,7 @@
         <v>44.99464</v>
       </c>
       <c r="H368">
-        <v>308.04828</v>
+        <v>308.0482788</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -18365,7 +18365,7 @@
         <v>28.82682</v>
       </c>
       <c r="H369">
-        <v>282.97563</v>
+        <v>282.9756329</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -18391,7 +18391,7 @@
         <v>32.47126</v>
       </c>
       <c r="H370">
-        <v>240.00909</v>
+        <v>240.0090897</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -18417,7 +18417,7 @@
         <v>213.22077</v>
       </c>
       <c r="H371">
-        <v>466.63417</v>
+        <v>466.6341664</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -18443,7 +18443,7 @@
         <v>208.15376</v>
       </c>
       <c r="H372">
-        <v>453.75606</v>
+        <v>453.7560555</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -18469,7 +18469,7 @@
         <v>208.65425</v>
       </c>
       <c r="H373">
-        <v>417.8995</v>
+        <v>417.8995047</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -18495,7 +18495,7 @@
         <v>145.9887</v>
       </c>
       <c r="H374">
-        <v>364.33902</v>
+        <v>364.3390164</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -18521,7 +18521,7 @@
         <v>207.17669</v>
       </c>
       <c r="H375">
-        <v>453.62983</v>
+        <v>453.6298253</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -18547,7 +18547,7 @@
         <v>109.8354</v>
       </c>
       <c r="H376">
-        <v>414.99842</v>
+        <v>414.9984179</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -18573,7 +18573,7 @@
         <v>81.14652</v>
       </c>
       <c r="H377">
-        <v>325.01213</v>
+        <v>325.0121338</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -18599,7 +18599,7 @@
         <v>236.35679</v>
       </c>
       <c r="H378">
-        <v>483.271</v>
+        <v>483.2710027</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -18625,7 +18625,7 @@
         <v>208.42812</v>
       </c>
       <c r="H379">
-        <v>451.23221</v>
+        <v>451.2322101</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -18651,7 +18651,7 @@
         <v>230.47986</v>
       </c>
       <c r="H380">
-        <v>433.0063</v>
+        <v>433.0063013</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -18677,7 +18677,7 @@
         <v>117.30251</v>
       </c>
       <c r="H381">
-        <v>381.07373</v>
+        <v>381.0737318</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -18703,7 +18703,7 @@
         <v>140.23576</v>
       </c>
       <c r="H382">
-        <v>424.10045</v>
+        <v>424.1004491</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -18729,7 +18729,7 @@
         <v>123.11411</v>
       </c>
       <c r="H383">
-        <v>282.87857</v>
+        <v>282.8785683</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -18755,7 +18755,7 @@
         <v>128.32857</v>
       </c>
       <c r="H384">
-        <v>345.28851</v>
+        <v>345.2885079</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -18807,7 +18807,7 @@
         <v>245.29488</v>
       </c>
       <c r="H386">
-        <v>438.43126</v>
+        <v>438.4312568</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -18833,7 +18833,7 @@
         <v>149.16346</v>
       </c>
       <c r="H387">
-        <v>314.48572</v>
+        <v>314.4857184</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -18859,7 +18859,7 @@
         <v>35.28787</v>
       </c>
       <c r="H388">
-        <v>161.114</v>
+        <v>161.1140017</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -18885,7 +18885,7 @@
         <v>51.38669</v>
       </c>
       <c r="H389">
-        <v>378.61791</v>
+        <v>378.6179128</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -18911,7 +18911,7 @@
         <v>40.4781</v>
       </c>
       <c r="H390">
-        <v>190.30179</v>
+        <v>190.3017858</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -18937,7 +18937,7 @@
         <v>39.4128</v>
       </c>
       <c r="H391">
-        <v>171.04011</v>
+        <v>171.0401107</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -18963,7 +18963,7 @@
         <v>211.01971</v>
       </c>
       <c r="H392">
-        <v>497.64688</v>
+        <v>497.6468768</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -18989,7 +18989,7 @@
         <v>214.78226</v>
       </c>
       <c r="H393">
-        <v>408.0797</v>
+        <v>408.0796979</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -19015,7 +19015,7 @@
         <v>131.37408</v>
       </c>
       <c r="H394">
-        <v>273.47879</v>
+        <v>273.4787903</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -19041,7 +19041,7 @@
         <v>86.51638</v>
       </c>
       <c r="H395">
-        <v>378.88131</v>
+        <v>378.8813066</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -19067,7 +19067,7 @@
         <v>29.98999</v>
       </c>
       <c r="H396">
-        <v>142.16015</v>
+        <v>142.1601453</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -19093,7 +19093,7 @@
         <v>24.99725</v>
       </c>
       <c r="H397">
-        <v>118.9768</v>
+        <v>118.9767969</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -19119,7 +19119,7 @@
         <v>68.25951999999999</v>
       </c>
       <c r="H398">
-        <v>258.56895</v>
+        <v>176.3106765</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -19145,7 +19145,7 @@
         <v>64.36573</v>
       </c>
       <c r="H399">
-        <v>227.07852</v>
+        <v>227.0785182</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -19171,7 +19171,7 @@
         <v>157.34745</v>
       </c>
       <c r="H400">
-        <v>492.73662</v>
+        <v>492.7366178</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -19197,7 +19197,7 @@
         <v>55.84824</v>
       </c>
       <c r="H401">
-        <v>280.79442</v>
+        <v>358.0734708</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -19223,7 +19223,7 @@
         <v>77.08172</v>
       </c>
       <c r="H402">
-        <v>284.18189</v>
+        <v>284.1818897</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -19249,7 +19249,7 @@
         <v>117.06552</v>
       </c>
       <c r="H403">
-        <v>345.80653</v>
+        <v>347.5921795</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -19275,7 +19275,7 @@
         <v>135.82662</v>
       </c>
       <c r="H404">
-        <v>299.67012</v>
+        <v>299.670119</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -19301,7 +19301,7 @@
         <v>59.25992</v>
       </c>
       <c r="H405">
-        <v>778.32782</v>
+        <v>778.3278198</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -19327,7 +19327,7 @@
         <v>16.07162</v>
       </c>
       <c r="H406">
-        <v>148.66048</v>
+        <v>148.6604843</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -19353,7 +19353,7 @@
         <v>114.75873</v>
       </c>
       <c r="H407">
-        <v>310.96721</v>
+        <v>310.967205</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -19379,7 +19379,7 @@
         <v>104.14854</v>
       </c>
       <c r="H408">
-        <v>420.88181</v>
+        <v>420.8818096</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -19405,7 +19405,7 @@
         <v>144.77596</v>
       </c>
       <c r="H409">
-        <v>427.65363</v>
+        <v>427.6536318</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -19431,7 +19431,7 @@
         <v>122.85792</v>
       </c>
       <c r="H410">
-        <v>341.69179</v>
+        <v>341.6917867</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -19457,7 +19457,7 @@
         <v>89.16482000000001</v>
       </c>
       <c r="H411">
-        <v>337.28412</v>
+        <v>337.2841153</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -19483,7 +19483,7 @@
         <v>73.9233</v>
       </c>
       <c r="H412">
-        <v>237.02133</v>
+        <v>174.9547794</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -19509,7 +19509,7 @@
         <v>96.28967</v>
       </c>
       <c r="H413">
-        <v>388.52595</v>
+        <v>388.5259534</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -19535,7 +19535,7 @@
         <v>96.37796</v>
       </c>
       <c r="H414">
-        <v>442.86401</v>
+        <v>442.8640148</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -19561,7 +19561,7 @@
         <v>39.61092</v>
       </c>
       <c r="H415">
-        <v>233.33104</v>
+        <v>233.3310385</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -19587,7 +19587,7 @@
         <v>121.87876</v>
       </c>
       <c r="H416">
-        <v>337.58889</v>
+        <v>337.5888915</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -19613,7 +19613,7 @@
         <v>79.26915</v>
       </c>
       <c r="H417">
-        <v>345.86824</v>
+        <v>345.8682423</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -19639,7 +19639,7 @@
         <v>44.47849</v>
       </c>
       <c r="H418">
-        <v>201.47988</v>
+        <v>201.4798846</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -19665,7 +19665,7 @@
         <v>61.39504</v>
       </c>
       <c r="H419">
-        <v>232.58331</v>
+        <v>232.5833056</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -19691,7 +19691,7 @@
         <v>80.53188</v>
       </c>
       <c r="H420">
-        <v>273.81053</v>
+        <v>273.8105325</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -19717,7 +19717,7 @@
         <v>91.52581000000001</v>
       </c>
       <c r="H421">
-        <v>383.55937</v>
+        <v>383.5593703</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -19743,7 +19743,7 @@
         <v>86.38157</v>
       </c>
       <c r="H422">
-        <v>314.33781</v>
+        <v>314.3378116</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -19769,7 +19769,7 @@
         <v>111.17372</v>
       </c>
       <c r="H423">
-        <v>414.53254</v>
+        <v>414.5325381</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -19795,7 +19795,7 @@
         <v>96.06406</v>
       </c>
       <c r="H424">
-        <v>525.05189</v>
+        <v>525.0518936</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -19821,7 +19821,7 @@
         <v>73.06701</v>
       </c>
       <c r="H425">
-        <v>379.00121</v>
+        <v>379.0012126</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -19847,7 +19847,7 @@
         <v>48.75803</v>
       </c>
       <c r="H426">
-        <v>294.59875</v>
+        <v>294.5987469</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -19873,7 +19873,7 @@
         <v>7.86442</v>
       </c>
       <c r="H427">
-        <v>66.40742</v>
+        <v>123.7599929</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -19899,7 +19899,7 @@
         <v>17.75537</v>
       </c>
       <c r="H428">
-        <v>150.44297</v>
+        <v>150.4429744</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -19925,7 +19925,7 @@
         <v>85.96117</v>
       </c>
       <c r="H429">
-        <v>273.66355</v>
+        <v>273.6635533</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -19951,7 +19951,7 @@
         <v>172.77295</v>
       </c>
       <c r="H430">
-        <v>389.67663</v>
+        <v>389.6766268</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -19977,7 +19977,7 @@
         <v>29.18792</v>
       </c>
       <c r="H431">
-        <v>172.80565</v>
+        <v>244.6668201</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -20003,7 +20003,7 @@
         <v>29.11002</v>
       </c>
       <c r="H432">
-        <v>146.0758</v>
+        <v>167.393389</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -20029,7 +20029,7 @@
         <v>42.44431</v>
       </c>
       <c r="H433">
-        <v>227.07278</v>
+        <v>227.0727804</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -20055,7 +20055,7 @@
         <v>107.56877</v>
       </c>
       <c r="H434">
-        <v>456.41435</v>
+        <v>456.414349</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -20081,7 +20081,7 @@
         <v>99.39229</v>
       </c>
       <c r="H435">
-        <v>463.58264</v>
+        <v>463.5826373</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -20107,7 +20107,7 @@
         <v>116.72141</v>
       </c>
       <c r="H436">
-        <v>517.23912</v>
+        <v>517.2391152</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -20133,7 +20133,7 @@
         <v>26.96219</v>
       </c>
       <c r="H437">
-        <v>195.31377</v>
+        <v>195.3137668</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -20159,7 +20159,7 @@
         <v>59.35258</v>
       </c>
       <c r="H438">
-        <v>293.18283</v>
+        <v>293.1828268</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -20185,7 +20185,7 @@
         <v>11.5069</v>
       </c>
       <c r="H439">
-        <v>140.07543</v>
+        <v>140.0754253</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -20211,7 +20211,7 @@
         <v>21.95915</v>
       </c>
       <c r="H440">
-        <v>135.43327</v>
+        <v>135.4332717</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -20237,7 +20237,7 @@
         <v>9.48474</v>
       </c>
       <c r="H441">
-        <v>73.94915</v>
+        <v>73.94914983</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -20263,7 +20263,7 @@
         <v>25.80811</v>
       </c>
       <c r="H442">
-        <v>186.94042</v>
+        <v>255.8276367</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -20289,7 +20289,7 @@
         <v>22.73509</v>
       </c>
       <c r="H443">
-        <v>145.41103</v>
+        <v>180.2136932</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -20315,7 +20315,7 @@
         <v>85.82015</v>
       </c>
       <c r="H444">
-        <v>297.1618</v>
+        <v>297.161804</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -20341,7 +20341,7 @@
         <v>106.51576</v>
       </c>
       <c r="H445">
-        <v>374.33895</v>
+        <v>374.3389473</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -20367,7 +20367,7 @@
         <v>36.50307</v>
       </c>
       <c r="H446">
-        <v>275.09594</v>
+        <v>275.095939</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -20393,7 +20393,7 @@
         <v>15.06214</v>
       </c>
       <c r="H447">
-        <v>128.51518</v>
+        <v>128.5151819</v>
       </c>
     </row>
     <row r="448" spans="1:8">
@@ -20419,7 +20419,7 @@
         <v>30.90818</v>
       </c>
       <c r="H448">
-        <v>146.51951</v>
+        <v>166.1673601</v>
       </c>
     </row>
     <row r="449" spans="1:8">
@@ -20445,7 +20445,7 @@
         <v>40.12486</v>
       </c>
       <c r="H449">
-        <v>161.77858</v>
+        <v>161.7785838</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -20471,7 +20471,7 @@
         <v>35.45489</v>
       </c>
       <c r="H450">
-        <v>141.19913</v>
+        <v>141.1991335</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -20497,7 +20497,7 @@
         <v>119.64084</v>
       </c>
       <c r="H451">
-        <v>342.31422</v>
+        <v>342.314217</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -20523,7 +20523,7 @@
         <v>27.88775</v>
       </c>
       <c r="H452">
-        <v>173.17244</v>
+        <v>173.1724409</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -20549,7 +20549,7 @@
         <v>165.17376</v>
       </c>
       <c r="H453">
-        <v>436.4185</v>
+        <v>436.4185006</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -20575,7 +20575,7 @@
         <v>33.01003</v>
       </c>
       <c r="H454">
-        <v>225.42708</v>
+        <v>283.7329861</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -20601,7 +20601,7 @@
         <v>28.22176</v>
       </c>
       <c r="H455">
-        <v>167.73094</v>
+        <v>167.7309425</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -20627,7 +20627,7 @@
         <v>378.21092</v>
       </c>
       <c r="H456">
-        <v>1344.04027</v>
+        <v>1344.040266</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -20653,7 +20653,7 @@
         <v>403.55663</v>
       </c>
       <c r="H457">
-        <v>1300.06594</v>
+        <v>1300.065936</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -20679,7 +20679,7 @@
         <v>18.42366</v>
       </c>
       <c r="H458">
-        <v>109.45848</v>
+        <v>124.6683144</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -20705,7 +20705,7 @@
         <v>23.55935</v>
       </c>
       <c r="H459">
-        <v>117.91529</v>
+        <v>115.3911583</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -20731,7 +20731,7 @@
         <v>139.65748</v>
       </c>
       <c r="H460">
-        <v>365.25163</v>
+        <v>365.2516285</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -20757,7 +20757,7 @@
         <v>28.02802</v>
       </c>
       <c r="H461">
-        <v>133.18621</v>
+        <v>133.1862104</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -20783,7 +20783,7 @@
         <v>64.86192</v>
       </c>
       <c r="H462">
-        <v>240.51245</v>
+        <v>169.2355718</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -20809,7 +20809,7 @@
         <v>71.99596</v>
       </c>
       <c r="H463">
-        <v>264.67011</v>
+        <v>263.8925799</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -20835,7 +20835,7 @@
         <v>34.52369</v>
       </c>
       <c r="H464">
-        <v>170.04776</v>
+        <v>230.4945241</v>
       </c>
     </row>
     <row r="465" spans="1:8">
@@ -20861,7 +20861,7 @@
         <v>29.13247</v>
       </c>
       <c r="H465">
-        <v>141.85575</v>
+        <v>141.8557547</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -20887,7 +20887,7 @@
         <v>62.38368</v>
       </c>
       <c r="H466">
-        <v>280.14713</v>
+        <v>218.6023847</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -20913,7 +20913,7 @@
         <v>27.95728</v>
       </c>
       <c r="H467">
-        <v>210.43435</v>
+        <v>210.4343532</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -20939,7 +20939,7 @@
         <v>22.14535</v>
       </c>
       <c r="H468">
-        <v>236.43746</v>
+        <v>236.4374601</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -20965,7 +20965,7 @@
         <v>20.56047</v>
       </c>
       <c r="H469">
-        <v>193.16903</v>
+        <v>202.7890368</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -20991,7 +20991,7 @@
         <v>21.17257</v>
       </c>
       <c r="H470">
-        <v>174.54457</v>
+        <v>200.841302</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -21017,7 +21017,7 @@
         <v>21.84039</v>
       </c>
       <c r="H471">
-        <v>213.21769</v>
+        <v>223.5941368</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -21043,7 +21043,7 @@
         <v>84.96271</v>
       </c>
       <c r="H472">
-        <v>398.39176</v>
+        <v>398.3917578</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -21069,7 +21069,7 @@
         <v>52.65318</v>
       </c>
       <c r="H473">
-        <v>264.86338</v>
+        <v>227.2134882</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -21095,7 +21095,7 @@
         <v>69.39613</v>
       </c>
       <c r="H474">
-        <v>291.38301</v>
+        <v>279.6437094</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -21121,7 +21121,7 @@
         <v>60.63341</v>
       </c>
       <c r="H475">
-        <v>235.75833</v>
+        <v>234.5835873</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -21147,7 +21147,7 @@
         <v>71.85527999999999</v>
       </c>
       <c r="H476">
-        <v>292.90813</v>
+        <v>283.0058837</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -21173,7 +21173,7 @@
         <v>60.27378</v>
       </c>
       <c r="H477">
-        <v>233.96968</v>
+        <v>233.9141716</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -21199,7 +21199,7 @@
         <v>82.21975999999999</v>
       </c>
       <c r="H478">
-        <v>441.80428</v>
+        <v>375.0933156</v>
       </c>
     </row>
     <row r="479" spans="1:8">
@@ -21225,7 +21225,7 @@
         <v>58.75249</v>
       </c>
       <c r="H479">
-        <v>233.39248</v>
+        <v>238.658973</v>
       </c>
     </row>
     <row r="480" spans="1:8">
@@ -21251,7 +21251,7 @@
         <v>69.26421000000001</v>
       </c>
       <c r="H480">
-        <v>352.22485</v>
+        <v>290.581707</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -21277,7 +21277,7 @@
         <v>176.71081</v>
       </c>
       <c r="H481">
-        <v>504.49741</v>
+        <v>504.4974081</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -21303,7 +21303,7 @@
         <v>8.96702</v>
       </c>
       <c r="H482">
-        <v>130.38685</v>
+        <v>130.3868457</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -21329,7 +21329,7 @@
         <v>32.0796</v>
       </c>
       <c r="H483">
-        <v>256.3435</v>
+        <v>244.6670342</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -21355,7 +21355,7 @@
         <v>31.75063</v>
       </c>
       <c r="H484">
-        <v>220.8396</v>
+        <v>242.8778991</v>
       </c>
     </row>
     <row r="485" spans="1:8">
@@ -21381,7 +21381,7 @@
         <v>87.13908000000001</v>
       </c>
       <c r="H485">
-        <v>415.01172</v>
+        <v>415.0117242</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -21407,7 +21407,7 @@
         <v>69.32389999999999</v>
       </c>
       <c r="H486">
-        <v>288.46453</v>
+        <v>230.4387823</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -21433,7 +21433,7 @@
         <v>70.35874</v>
       </c>
       <c r="H487">
-        <v>286.73159</v>
+        <v>227.6031447</v>
       </c>
     </row>
     <row r="488" spans="1:8">
@@ -21459,7 +21459,7 @@
         <v>59.72855</v>
       </c>
       <c r="H488">
-        <v>232.6546</v>
+        <v>175.3730984</v>
       </c>
     </row>
     <row r="489" spans="1:8">
@@ -21485,7 +21485,7 @@
         <v>74.90924</v>
       </c>
       <c r="H489">
-        <v>291.06398</v>
+        <v>232.7599474</v>
       </c>
     </row>
     <row r="490" spans="1:8">
@@ -21511,7 +21511,7 @@
         <v>62.07712</v>
       </c>
       <c r="H490">
-        <v>286.9241</v>
+        <v>235.0523536</v>
       </c>
     </row>
     <row r="491" spans="1:8">
@@ -21537,7 +21537,7 @@
         <v>78.07187</v>
       </c>
       <c r="H491">
-        <v>412.91678</v>
+        <v>399.142416</v>
       </c>
     </row>
     <row r="492" spans="1:8">
@@ -21563,7 +21563,7 @@
         <v>64.59</v>
       </c>
       <c r="H492">
-        <v>287.65445</v>
+        <v>232.711462</v>
       </c>
     </row>
     <row r="493" spans="1:8">
@@ -21589,7 +21589,7 @@
         <v>53.74947</v>
       </c>
       <c r="H493">
-        <v>226.737</v>
+        <v>174.5014575</v>
       </c>
     </row>
     <row r="494" spans="1:8">
@@ -21615,7 +21615,7 @@
         <v>68.39543</v>
       </c>
       <c r="H494">
-        <v>289.2649</v>
+        <v>231.6566894</v>
       </c>
     </row>
     <row r="495" spans="1:8">
@@ -21641,7 +21641,7 @@
         <v>58.3172</v>
       </c>
       <c r="H495">
-        <v>232.45981</v>
+        <v>176.802832</v>
       </c>
     </row>
     <row r="496" spans="1:8">
@@ -21667,7 +21667,7 @@
         <v>83.4235</v>
       </c>
       <c r="H496">
-        <v>418.08536</v>
+        <v>418.0853566</v>
       </c>
     </row>
     <row r="497" spans="1:8">
@@ -21693,7 +21693,7 @@
         <v>71.72757</v>
       </c>
       <c r="H497">
-        <v>288.24877</v>
+        <v>228.8081027</v>
       </c>
     </row>
     <row r="498" spans="1:8">
@@ -21719,7 +21719,7 @@
         <v>31.84421</v>
       </c>
       <c r="H498">
-        <v>186.83909</v>
+        <v>186.8390901</v>
       </c>
     </row>
     <row r="499" spans="1:8">
@@ -21745,7 +21745,7 @@
         <v>70.47083000000001</v>
       </c>
       <c r="H499">
-        <v>259.91896</v>
+        <v>259.9189582</v>
       </c>
     </row>
     <row r="500" spans="1:8">
@@ -21771,7 +21771,7 @@
         <v>42.04222</v>
       </c>
       <c r="H500">
-        <v>193.59901</v>
+        <v>193.5990078</v>
       </c>
     </row>
     <row r="501" spans="1:8">
@@ -21797,7 +21797,7 @@
         <v>54.12606</v>
       </c>
       <c r="H501">
-        <v>208.08826</v>
+        <v>191.486862</v>
       </c>
     </row>
     <row r="502" spans="1:8">
@@ -21823,7 +21823,7 @@
         <v>56.55144</v>
       </c>
       <c r="H502">
-        <v>210.88971</v>
+        <v>190.9703064</v>
       </c>
     </row>
     <row r="503" spans="1:8">
@@ -21849,7 +21849,7 @@
         <v>46.07356</v>
       </c>
       <c r="H503">
-        <v>201.83174</v>
+        <v>186.8037348</v>
       </c>
     </row>
     <row r="504" spans="1:8">
@@ -21875,7 +21875,7 @@
         <v>28.63256</v>
       </c>
       <c r="H504">
-        <v>137.30735</v>
+        <v>137.3073517</v>
       </c>
     </row>
     <row r="505" spans="1:8">
@@ -21901,7 +21901,7 @@
         <v>51.81784</v>
       </c>
       <c r="H505">
-        <v>207.08804</v>
+        <v>190.3951927</v>
       </c>
     </row>
     <row r="506" spans="1:8">
@@ -21927,7 +21927,7 @@
         <v>62.06915</v>
       </c>
       <c r="H506">
-        <v>218.75446</v>
+        <v>210.8251866</v>
       </c>
     </row>
     <row r="507" spans="1:8">
@@ -21953,7 +21953,7 @@
         <v>63.7289</v>
       </c>
       <c r="H507">
-        <v>296.85683</v>
+        <v>296.8568284</v>
       </c>
     </row>
     <row r="508" spans="1:8">
@@ -21979,7 +21979,7 @@
         <v>79.90172</v>
       </c>
       <c r="H508">
-        <v>474.90839</v>
+        <v>474.9083941</v>
       </c>
     </row>
     <row r="509" spans="1:8">
@@ -22005,7 +22005,7 @@
         <v>35.48753</v>
       </c>
       <c r="H509">
-        <v>188.90109</v>
+        <v>188.9010918</v>
       </c>
     </row>
     <row r="510" spans="1:8">
@@ -22031,7 +22031,7 @@
         <v>40.77757</v>
       </c>
       <c r="H510">
-        <v>188.31732</v>
+        <v>188.3173155</v>
       </c>
     </row>
     <row r="511" spans="1:8">
@@ -22057,7 +22057,7 @@
         <v>71.14687000000001</v>
       </c>
       <c r="H511">
-        <v>239.80781</v>
+        <v>239.8078118</v>
       </c>
     </row>
     <row r="512" spans="1:8">
@@ -22083,7 +22083,7 @@
         <v>278.86681</v>
       </c>
       <c r="H512">
-        <v>553.68226</v>
+        <v>553.6822557</v>
       </c>
     </row>
     <row r="513" spans="1:8">
@@ -22109,7 +22109,7 @@
         <v>271.37202</v>
       </c>
       <c r="H513">
-        <v>519.32366</v>
+        <v>519.323656</v>
       </c>
     </row>
     <row r="514" spans="1:8">
@@ -22135,7 +22135,7 @@
         <v>316.61642</v>
       </c>
       <c r="H514">
-        <v>608.17499</v>
+        <v>608.1749888000001</v>
       </c>
     </row>
     <row r="515" spans="1:8">
@@ -22161,7 +22161,7 @@
         <v>41.2083</v>
       </c>
       <c r="H515">
-        <v>170.77321</v>
+        <v>170.773212</v>
       </c>
     </row>
     <row r="516" spans="1:8">
@@ -22187,7 +22187,7 @@
         <v>40.82757</v>
       </c>
       <c r="H516">
-        <v>182.12989</v>
+        <v>182.1298937</v>
       </c>
     </row>
     <row r="517" spans="1:8">
@@ -22213,7 +22213,7 @@
         <v>85.55409</v>
       </c>
       <c r="H517">
-        <v>355.5806</v>
+        <v>355.5806049</v>
       </c>
     </row>
     <row r="518" spans="1:8">
@@ -22239,7 +22239,7 @@
         <v>45.10072</v>
       </c>
       <c r="H518">
-        <v>256.92866</v>
+        <v>256.9286576</v>
       </c>
     </row>
     <row r="519" spans="1:8">
@@ -22265,7 +22265,7 @@
         <v>37.71603</v>
       </c>
       <c r="H519">
-        <v>203.31967</v>
+        <v>203.3196715</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -22291,7 +22291,7 @@
         <v>36.0514</v>
       </c>
       <c r="H520">
-        <v>298.19031</v>
+        <v>298.1903138</v>
       </c>
     </row>
     <row r="521" spans="1:8">
@@ -22317,7 +22317,7 @@
         <v>37.34911</v>
       </c>
       <c r="H521">
-        <v>298.20875</v>
+        <v>266.6415064</v>
       </c>
     </row>
     <row r="522" spans="1:8">
@@ -22343,7 +22343,7 @@
         <v>47.02667</v>
       </c>
       <c r="H522">
-        <v>253.56476</v>
+        <v>203.0663321</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -22369,7 +22369,7 @@
         <v>46.78674</v>
       </c>
       <c r="H523">
-        <v>219.14675</v>
+        <v>219.1467511</v>
       </c>
     </row>
     <row r="524" spans="1:8">
@@ -22395,7 +22395,7 @@
         <v>177.81113</v>
       </c>
       <c r="H524">
-        <v>923.0355499999999</v>
+        <v>923.0355481</v>
       </c>
     </row>
     <row r="525" spans="1:8">
@@ -22421,7 +22421,7 @@
         <v>123.05946</v>
       </c>
       <c r="H525">
-        <v>252.76648</v>
+        <v>190.1737744</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -22447,7 +22447,7 @@
         <v>156.68623</v>
       </c>
       <c r="H526">
-        <v>364.45592</v>
+        <v>364.4559188</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -22473,7 +22473,7 @@
         <v>259.54052</v>
       </c>
       <c r="H527">
-        <v>583.63822</v>
+        <v>583.6382225</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -22499,7 +22499,7 @@
         <v>252.53842</v>
       </c>
       <c r="H528">
-        <v>566.14036</v>
+        <v>566.1403582</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -22525,7 +22525,7 @@
         <v>332.13024</v>
       </c>
       <c r="H529">
-        <v>580.53256</v>
+        <v>541.9906120000001</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -22551,7 +22551,7 @@
         <v>132.69432</v>
       </c>
       <c r="H530">
-        <v>269.98248</v>
+        <v>194.103452</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -22577,7 +22577,7 @@
         <v>130.31606</v>
       </c>
       <c r="H531">
-        <v>262.29578</v>
+        <v>189.9002653</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -22603,7 +22603,7 @@
         <v>244.58376</v>
       </c>
       <c r="H532">
-        <v>637.44377</v>
+        <v>652.7010406000001</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -22629,7 +22629,7 @@
         <v>149.66419</v>
       </c>
       <c r="H533">
-        <v>430.39034</v>
+        <v>430.3903388</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -22655,7 +22655,7 @@
         <v>131.5694</v>
       </c>
       <c r="H534">
-        <v>291.46652</v>
+        <v>239.4631893</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -22681,7 +22681,7 @@
         <v>120.93702</v>
       </c>
       <c r="H535">
-        <v>247.05755</v>
+        <v>247.057553</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -22707,7 +22707,7 @@
         <v>86.86264</v>
       </c>
       <c r="H536">
-        <v>209.98563</v>
+        <v>209.9856312</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -22733,7 +22733,7 @@
         <v>102.70292</v>
       </c>
       <c r="H537">
-        <v>351.79599</v>
+        <v>351.7959885</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -22759,7 +22759,7 @@
         <v>83.01533000000001</v>
       </c>
       <c r="H538">
-        <v>423.33781</v>
+        <v>349.9967783</v>
       </c>
     </row>
     <row r="539" spans="1:8">
@@ -22785,7 +22785,7 @@
         <v>249.01921</v>
       </c>
       <c r="H539">
-        <v>545.73849</v>
+        <v>545.7384867</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -22811,7 +22811,7 @@
         <v>301.06407</v>
       </c>
       <c r="H540">
-        <v>441.0459</v>
+        <v>441.0458989</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -22837,7 +22837,7 @@
         <v>250.34856</v>
       </c>
       <c r="H541">
-        <v>390.29143</v>
+        <v>390.2914293</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -22863,7 +22863,7 @@
         <v>259.38424</v>
       </c>
       <c r="H542">
-        <v>569.46964</v>
+        <v>569.4696433</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -22889,7 +22889,7 @@
         <v>250.12025</v>
       </c>
       <c r="H543">
-        <v>486.66834</v>
+        <v>486.6683362</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -22915,7 +22915,7 @@
         <v>17.03372</v>
       </c>
       <c r="H544">
-        <v>135.90432</v>
+        <v>142.5090842</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -22941,7 +22941,7 @@
         <v>256.90475</v>
       </c>
       <c r="H545">
-        <v>531.3390000000001</v>
+        <v>531.3389971</v>
       </c>
     </row>
     <row r="546" spans="1:8">
@@ -22967,7 +22967,7 @@
         <v>67.30611</v>
       </c>
       <c r="H546">
-        <v>302.42655</v>
+        <v>229.478644</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -22993,7 +22993,7 @@
         <v>308.8625</v>
       </c>
       <c r="H547">
-        <v>660.4867400000001</v>
+        <v>660.486736</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -23019,7 +23019,7 @@
         <v>265.72137</v>
       </c>
       <c r="H548">
-        <v>522.6017399999999</v>
+        <v>522.6017412</v>
       </c>
     </row>
     <row r="549" spans="1:8">
@@ -23071,7 +23071,7 @@
         <v>123.74069</v>
       </c>
       <c r="H550">
-        <v>442.9212</v>
+        <v>442.9212028</v>
       </c>
     </row>
     <row r="551" spans="1:8">
@@ -23097,7 +23097,7 @@
         <v>88.11346</v>
       </c>
       <c r="H551">
-        <v>265.45067</v>
+        <v>223.80989</v>
       </c>
     </row>
     <row r="552" spans="1:8">
@@ -23123,7 +23123,7 @@
         <v>92.04227</v>
       </c>
       <c r="H552">
-        <v>302.2502</v>
+        <v>302.2501978</v>
       </c>
     </row>
     <row r="553" spans="1:8">
@@ -23149,7 +23149,7 @@
         <v>70.88160000000001</v>
       </c>
       <c r="H553">
-        <v>312.06247</v>
+        <v>242.8997585</v>
       </c>
     </row>
     <row r="554" spans="1:8">
@@ -23175,7 +23175,7 @@
         <v>83.89075</v>
       </c>
       <c r="H554">
-        <v>232.09776</v>
+        <v>163.7009435</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -23201,7 +23201,7 @@
         <v>28.52299</v>
       </c>
       <c r="H555">
-        <v>155.60802</v>
+        <v>247.5963167</v>
       </c>
     </row>
     <row r="556" spans="1:8">
@@ -23227,7 +23227,7 @@
         <v>127.16849</v>
       </c>
       <c r="H556">
-        <v>309.0917</v>
+        <v>309.0916988</v>
       </c>
     </row>
     <row r="557" spans="1:8">
@@ -23253,7 +23253,7 @@
         <v>302.66279</v>
       </c>
       <c r="H557">
-        <v>587.60748</v>
+        <v>587.6074826</v>
       </c>
     </row>
     <row r="558" spans="1:8">
@@ -23279,7 +23279,7 @@
         <v>29.62086</v>
       </c>
       <c r="H558">
-        <v>212.60457</v>
+        <v>231.5861501</v>
       </c>
     </row>
     <row r="559" spans="1:8">
@@ -23305,7 +23305,7 @@
         <v>195.27244</v>
       </c>
       <c r="H559">
-        <v>325.98201</v>
+        <v>244.234259</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -23331,7 +23331,7 @@
         <v>174.7411</v>
       </c>
       <c r="H560">
-        <v>313.69325</v>
+        <v>231.7312831</v>
       </c>
     </row>
     <row r="561" spans="1:8">
@@ -23357,7 +23357,7 @@
         <v>210.84677</v>
       </c>
       <c r="H561">
-        <v>371.75149</v>
+        <v>371.7514892</v>
       </c>
     </row>
     <row r="562" spans="1:8">
@@ -23383,7 +23383,7 @@
         <v>19.284</v>
       </c>
       <c r="H562">
-        <v>132.61501</v>
+        <v>132.6150073</v>
       </c>
     </row>
     <row r="563" spans="1:8">
@@ -23409,7 +23409,7 @@
         <v>112.19264</v>
       </c>
       <c r="H563">
-        <v>520.91544</v>
+        <v>520.9154357</v>
       </c>
     </row>
     <row r="564" spans="1:8">
@@ -23435,7 +23435,7 @@
         <v>63.5129</v>
       </c>
       <c r="H564">
-        <v>332.96205</v>
+        <v>332.9620483</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -23461,7 +23461,7 @@
         <v>15.83426</v>
       </c>
       <c r="H565">
-        <v>189.74769</v>
+        <v>189.7476949</v>
       </c>
     </row>
     <row r="566" spans="1:8">
@@ -23487,7 +23487,7 @@
         <v>54.10381</v>
       </c>
       <c r="H566">
-        <v>262.81927</v>
+        <v>262.8192686</v>
       </c>
     </row>
     <row r="567" spans="1:8">
@@ -23513,7 +23513,7 @@
         <v>80.06180000000001</v>
       </c>
       <c r="H567">
-        <v>648.8222500000001</v>
+        <v>648.8222491</v>
       </c>
     </row>
     <row r="568" spans="1:8">
@@ -23539,7 +23539,7 @@
         <v>139.37315</v>
       </c>
       <c r="H568">
-        <v>479.44942</v>
+        <v>467.3828993</v>
       </c>
     </row>
     <row r="569" spans="1:8">
@@ -23565,7 +23565,7 @@
         <v>30.93125</v>
       </c>
       <c r="H569">
-        <v>168.57268</v>
+        <v>168.5726751</v>
       </c>
     </row>
     <row r="570" spans="1:8">
@@ -23591,7 +23591,7 @@
         <v>37.23</v>
       </c>
       <c r="H570">
-        <v>335.58636</v>
+        <v>335.5863627</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -23617,7 +23617,7 @@
         <v>120.7399</v>
       </c>
       <c r="H571">
-        <v>432.77612</v>
+        <v>429.6234806</v>
       </c>
     </row>
     <row r="572" spans="1:8">
@@ -23643,7 +23643,7 @@
         <v>96.50332</v>
       </c>
       <c r="H572">
-        <v>320.85375</v>
+        <v>313.3003676</v>
       </c>
     </row>
     <row r="573" spans="1:8">
@@ -23669,7 +23669,7 @@
         <v>36.37125</v>
       </c>
       <c r="H573">
-        <v>313.28813</v>
+        <v>272.9801536</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -23695,7 +23695,7 @@
         <v>30.26918</v>
       </c>
       <c r="H574">
-        <v>214.13687</v>
+        <v>168.3818421</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -23721,7 +23721,7 @@
         <v>33.91995</v>
       </c>
       <c r="H575">
-        <v>216.568</v>
+        <v>216.5679975</v>
       </c>
     </row>
     <row r="576" spans="1:8">
@@ -23747,7 +23747,7 @@
         <v>35.02354</v>
       </c>
       <c r="H576">
-        <v>179.8213</v>
+        <v>179.8213041</v>
       </c>
     </row>
     <row r="577" spans="1:8">
@@ -23773,7 +23773,7 @@
         <v>74.90721000000001</v>
       </c>
       <c r="H577">
-        <v>276.98412</v>
+        <v>276.984122</v>
       </c>
     </row>
     <row r="578" spans="1:8">
@@ -23799,7 +23799,7 @@
         <v>267.99624</v>
       </c>
       <c r="H578">
-        <v>561.48272</v>
+        <v>561.4827235</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -23825,7 +23825,7 @@
         <v>72.58408</v>
       </c>
       <c r="H579">
-        <v>263.7584</v>
+        <v>298.3040064</v>
       </c>
     </row>
     <row r="580" spans="1:8">
@@ -23851,7 +23851,7 @@
         <v>114.61746</v>
       </c>
       <c r="H580">
-        <v>321.96251</v>
+        <v>321.9625098</v>
       </c>
     </row>
     <row r="581" spans="1:8">
@@ -23877,7 +23877,7 @@
         <v>174.89511</v>
       </c>
       <c r="H581">
-        <v>441.88836</v>
+        <v>441.8883604</v>
       </c>
     </row>
     <row r="582" spans="1:8">
@@ -23903,7 +23903,7 @@
         <v>87.43127</v>
       </c>
       <c r="H582">
-        <v>297.12449</v>
+        <v>297.1244909</v>
       </c>
     </row>
     <row r="583" spans="1:8">
@@ -23929,7 +23929,7 @@
         <v>111.95982</v>
       </c>
       <c r="H583">
-        <v>369.92748</v>
+        <v>369.9274762</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -23955,7 +23955,7 @@
         <v>86.76528</v>
       </c>
       <c r="H584">
-        <v>401.03277</v>
+        <v>401.0327681</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -23981,7 +23981,7 @@
         <v>222.1743</v>
       </c>
       <c r="H585">
-        <v>611.0764</v>
+        <v>611.0763977</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -24007,7 +24007,7 @@
         <v>133.01434</v>
       </c>
       <c r="H586">
-        <v>336.53194</v>
+        <v>336.5319382</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -24033,7 +24033,7 @@
         <v>267.25632</v>
       </c>
       <c r="H587">
-        <v>640.77167</v>
+        <v>620.0999164999999</v>
       </c>
     </row>
     <row r="588" spans="1:8">
@@ -24059,7 +24059,7 @@
         <v>39.23017</v>
       </c>
       <c r="H588">
-        <v>270.68488</v>
+        <v>270.684875</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -24085,7 +24085,7 @@
         <v>49.85393</v>
       </c>
       <c r="H589">
-        <v>213.05647</v>
+        <v>213.0564739</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -24111,7 +24111,7 @@
         <v>41.10496</v>
       </c>
       <c r="H590">
-        <v>167.78424</v>
+        <v>167.7842402</v>
       </c>
     </row>
     <row r="591" spans="1:8">
@@ -24137,7 +24137,7 @@
         <v>169.44318</v>
       </c>
       <c r="H591">
-        <v>384.28572</v>
+        <v>384.2857186</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -24163,7 +24163,7 @@
         <v>202.41931</v>
       </c>
       <c r="H592">
-        <v>481.35967</v>
+        <v>481.3596733</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -24189,7 +24189,7 @@
         <v>100.67522</v>
       </c>
       <c r="H593">
-        <v>306.65143</v>
+        <v>295.4614312</v>
       </c>
     </row>
     <row r="594" spans="1:8">
@@ -24215,7 +24215,7 @@
         <v>95.93601</v>
       </c>
       <c r="H594">
-        <v>274.41081</v>
+        <v>269.4441582</v>
       </c>
     </row>
     <row r="595" spans="1:8">
@@ -24241,7 +24241,7 @@
         <v>82.49959</v>
       </c>
       <c r="H595">
-        <v>223.09864</v>
+        <v>181.4225158</v>
       </c>
     </row>
     <row r="596" spans="1:8">
@@ -24267,7 +24267,7 @@
         <v>9.54555</v>
       </c>
       <c r="H596">
-        <v>341.44641</v>
+        <v>341.4464098</v>
       </c>
     </row>
     <row r="597" spans="1:8">
@@ -24293,7 +24293,7 @@
         <v>17.83558</v>
       </c>
       <c r="H597">
-        <v>137.97187</v>
+        <v>153.5795891</v>
       </c>
     </row>
     <row r="598" spans="1:8">
@@ -24319,7 +24319,7 @@
         <v>129.24758</v>
       </c>
       <c r="H598">
-        <v>353.90627</v>
+        <v>353.906267</v>
       </c>
     </row>
     <row r="599" spans="1:8">
@@ -24345,7 +24345,7 @@
         <v>120.2473</v>
       </c>
       <c r="H599">
-        <v>313.2626</v>
+        <v>313.2626003</v>
       </c>
     </row>
     <row r="600" spans="1:8">
@@ -24371,7 +24371,7 @@
         <v>215.24556</v>
       </c>
       <c r="H600">
-        <v>362.39203</v>
+        <v>315.5942215</v>
       </c>
     </row>
     <row r="601" spans="1:8">
@@ -24397,7 +24397,7 @@
         <v>83.84141</v>
       </c>
       <c r="H601">
-        <v>240.72765</v>
+        <v>240.7276451</v>
       </c>
     </row>
     <row r="602" spans="1:8">
@@ -24423,7 +24423,7 @@
         <v>84.76898</v>
       </c>
       <c r="H602">
-        <v>238.46014</v>
+        <v>238.4601447</v>
       </c>
     </row>
     <row r="603" spans="1:8">
@@ -24449,7 +24449,7 @@
         <v>16.91038</v>
       </c>
       <c r="H603">
-        <v>99.85456000000001</v>
+        <v>113.8022173</v>
       </c>
     </row>
     <row r="604" spans="1:8">
@@ -24475,7 +24475,7 @@
         <v>9.969749999999999</v>
       </c>
       <c r="H604">
-        <v>316.84841</v>
+        <v>316.8484137</v>
       </c>
     </row>
     <row r="605" spans="1:8">
@@ -24501,7 +24501,7 @@
         <v>316.63289</v>
       </c>
       <c r="H605">
-        <v>693.28871</v>
+        <v>693.2887064</v>
       </c>
     </row>
     <row r="606" spans="1:8">
@@ -24527,7 +24527,7 @@
         <v>274.16971</v>
       </c>
       <c r="H606">
-        <v>693.74076</v>
+        <v>640.0289418999999</v>
       </c>
     </row>
     <row r="607" spans="1:8">
@@ -24553,7 +24553,7 @@
         <v>189.45638</v>
       </c>
       <c r="H607">
-        <v>570.18551</v>
+        <v>513.0133832</v>
       </c>
     </row>
     <row r="608" spans="1:8">
@@ -24579,7 +24579,7 @@
         <v>280.1361</v>
       </c>
       <c r="H608">
-        <v>516.7190000000001</v>
+        <v>516.719001</v>
       </c>
     </row>
     <row r="609" spans="1:8">
@@ -24605,7 +24605,7 @@
         <v>239.22913</v>
       </c>
       <c r="H609">
-        <v>574.51875</v>
+        <v>489.8286642</v>
       </c>
     </row>
     <row r="610" spans="1:8">
@@ -24631,7 +24631,7 @@
         <v>264.45452</v>
       </c>
       <c r="H610">
-        <v>613.58153</v>
+        <v>613.5815342</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -24657,7 +24657,7 @@
         <v>183.456</v>
       </c>
       <c r="H611">
-        <v>530.90344</v>
+        <v>530.9034448</v>
       </c>
     </row>
     <row r="612" spans="1:8">
@@ -24683,7 +24683,7 @@
         <v>236.26752</v>
       </c>
       <c r="H612">
-        <v>616.3292</v>
+        <v>548.8560123</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -24709,7 +24709,7 @@
         <v>102.36374</v>
       </c>
       <c r="H613">
-        <v>305.23885</v>
+        <v>305.2388471</v>
       </c>
     </row>
     <row r="614" spans="1:8">
@@ -24735,7 +24735,7 @@
         <v>337.03099</v>
       </c>
       <c r="H614">
-        <v>514.61383</v>
+        <v>465.7834321</v>
       </c>
     </row>
     <row r="615" spans="1:8">
@@ -24761,7 +24761,7 @@
         <v>288.39688</v>
       </c>
       <c r="H615">
-        <v>475.19645</v>
+        <v>475.1964513</v>
       </c>
     </row>
     <row r="616" spans="1:8">
@@ -24787,7 +24787,7 @@
         <v>294.98015</v>
       </c>
       <c r="H616">
-        <v>596.51695</v>
+        <v>586.9031125</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -24813,7 +24813,7 @@
         <v>226.93939</v>
       </c>
       <c r="H617">
-        <v>429.34863</v>
+        <v>423.4614874</v>
       </c>
     </row>
     <row r="618" spans="1:8">
@@ -24839,7 +24839,7 @@
         <v>170.71502</v>
       </c>
       <c r="H618">
-        <v>786.85126</v>
+        <v>786.851265</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -24865,7 +24865,7 @@
         <v>105.16752</v>
       </c>
       <c r="H619">
-        <v>662.91249</v>
+        <v>662.9124882</v>
       </c>
     </row>
     <row r="620" spans="1:8">
@@ -24891,7 +24891,7 @@
         <v>15.12788</v>
       </c>
       <c r="H620">
-        <v>214.79679</v>
+        <v>214.7967907</v>
       </c>
     </row>
     <row r="621" spans="1:8">
@@ -24917,7 +24917,7 @@
         <v>63.7032</v>
       </c>
       <c r="H621">
-        <v>299.63641</v>
+        <v>299.6364054</v>
       </c>
     </row>
     <row r="622" spans="1:8">
@@ -24943,7 +24943,7 @@
         <v>54.6681</v>
       </c>
       <c r="H622">
-        <v>236.05931</v>
+        <v>236.0593129</v>
       </c>
     </row>
     <row r="623" spans="1:8">
@@ -24969,7 +24969,7 @@
         <v>58.43446</v>
       </c>
       <c r="H623">
-        <v>265.50681</v>
+        <v>296.4034593</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -24995,7 +24995,7 @@
         <v>56.3405</v>
       </c>
       <c r="H624">
-        <v>220.9146</v>
+        <v>181.9225055</v>
       </c>
     </row>
     <row r="625" spans="1:8">
@@ -25021,7 +25021,7 @@
         <v>62.87987</v>
       </c>
       <c r="H625">
-        <v>311.20985</v>
+        <v>321.1234607</v>
       </c>
     </row>
     <row r="626" spans="1:8">
@@ -25047,7 +25047,7 @@
         <v>52.55395</v>
       </c>
       <c r="H626">
-        <v>236.65039</v>
+        <v>241.5600765</v>
       </c>
     </row>
     <row r="627" spans="1:8">
@@ -25073,7 +25073,7 @@
         <v>161.57966</v>
       </c>
       <c r="H627">
-        <v>719.30244</v>
+        <v>719.3024358</v>
       </c>
     </row>
     <row r="628" spans="1:8">
@@ -25099,7 +25099,7 @@
         <v>129.89428</v>
       </c>
       <c r="H628">
-        <v>453.91884</v>
+        <v>453.9188409</v>
       </c>
     </row>
     <row r="629" spans="1:8">
@@ -25125,7 +25125,7 @@
         <v>42.91008</v>
       </c>
       <c r="H629">
-        <v>166.10191</v>
+        <v>249.2228137</v>
       </c>
     </row>
     <row r="630" spans="1:8">
@@ -25151,7 +25151,7 @@
         <v>80.65949000000001</v>
       </c>
       <c r="H630">
-        <v>292.65769</v>
+        <v>292.6576919</v>
       </c>
     </row>
     <row r="631" spans="1:8">
@@ -25177,7 +25177,7 @@
         <v>102.29286</v>
       </c>
       <c r="H631">
-        <v>595.64343</v>
+        <v>595.6434308</v>
       </c>
     </row>
     <row r="632" spans="1:8">
@@ -25203,7 +25203,7 @@
         <v>120.78559</v>
       </c>
       <c r="H632">
-        <v>492.03043</v>
+        <v>492.0304334</v>
       </c>
     </row>
     <row r="633" spans="1:8">
@@ -25229,7 +25229,7 @@
         <v>106.50762</v>
       </c>
       <c r="H633">
-        <v>262.04657</v>
+        <v>311.0187329</v>
       </c>
     </row>
     <row r="634" spans="1:8">
@@ -25255,7 +25255,7 @@
         <v>119.39097</v>
       </c>
       <c r="H634">
-        <v>545.00384</v>
+        <v>545.003841</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -25281,7 +25281,7 @@
         <v>364.383</v>
       </c>
       <c r="H635">
-        <v>1062.7228</v>
+        <v>1062.722796</v>
       </c>
     </row>
     <row r="636" spans="1:8">
@@ -25307,7 +25307,7 @@
         <v>126.08435</v>
       </c>
       <c r="H636">
-        <v>429.04379</v>
+        <v>429.0437906</v>
       </c>
     </row>
     <row r="637" spans="1:8">
@@ -25333,7 +25333,7 @@
         <v>70.51219</v>
       </c>
       <c r="H637">
-        <v>268.58748</v>
+        <v>268.5874784</v>
       </c>
     </row>
     <row r="638" spans="1:8">
@@ -25359,7 +25359,7 @@
         <v>91.05578</v>
       </c>
       <c r="H638">
-        <v>322.51069</v>
+        <v>246.6422698</v>
       </c>
     </row>
     <row r="639" spans="1:8">
@@ -25385,7 +25385,7 @@
         <v>1.61888</v>
       </c>
       <c r="H639">
-        <v>180.08394</v>
+        <v>180.0839425</v>
       </c>
     </row>
     <row r="640" spans="1:8">
@@ -25411,7 +25411,7 @@
         <v>12.35239</v>
       </c>
       <c r="H640">
-        <v>147.46658</v>
+        <v>147.4665758</v>
       </c>
     </row>
     <row r="641" spans="1:8">
@@ -25437,7 +25437,7 @@
         <v>15.07274</v>
       </c>
       <c r="H641">
-        <v>133.07557</v>
+        <v>133.0755675</v>
       </c>
     </row>
     <row r="642" spans="1:8">
@@ -25463,7 +25463,7 @@
         <v>19.63991</v>
       </c>
       <c r="H642">
-        <v>111.66442</v>
+        <v>111.6644209</v>
       </c>
     </row>
     <row r="643" spans="1:8">
@@ -25489,7 +25489,7 @@
         <v>19.07486</v>
       </c>
       <c r="H643">
-        <v>121.14029</v>
+        <v>121.140293</v>
       </c>
     </row>
     <row r="644" spans="1:8">
@@ -25515,7 +25515,7 @@
         <v>19.73607</v>
       </c>
       <c r="H644">
-        <v>112.9635</v>
+        <v>188.8075238</v>
       </c>
     </row>
     <row r="645" spans="1:8">
@@ -25541,7 +25541,7 @@
         <v>147.36358</v>
       </c>
       <c r="H645">
-        <v>304.9922</v>
+        <v>304.9922021</v>
       </c>
     </row>
     <row r="646" spans="1:8">
@@ -25567,7 +25567,7 @@
         <v>107.88365</v>
       </c>
       <c r="H646">
-        <v>348.30108</v>
+        <v>348.3010758</v>
       </c>
     </row>
     <row r="647" spans="1:8">
@@ -25593,7 +25593,7 @@
         <v>67.41625999999999</v>
       </c>
       <c r="H647">
-        <v>323.92035</v>
+        <v>323.9203515</v>
       </c>
     </row>
     <row r="648" spans="1:8">
@@ -25619,7 +25619,7 @@
         <v>86.63327</v>
       </c>
       <c r="H648">
-        <v>445.42091</v>
+        <v>445.4209148</v>
       </c>
     </row>
     <row r="649" spans="1:8">
@@ -25645,7 +25645,7 @@
         <v>99.77198</v>
       </c>
       <c r="H649">
-        <v>329.39819</v>
+        <v>329.398187</v>
       </c>
     </row>
     <row r="650" spans="1:8">
@@ -25671,7 +25671,7 @@
         <v>71.75091</v>
       </c>
       <c r="H650">
-        <v>595.65306</v>
+        <v>595.6530552</v>
       </c>
     </row>
     <row r="651" spans="1:8">
@@ -25697,7 +25697,7 @@
         <v>110.82684</v>
       </c>
       <c r="H651">
-        <v>463.62048</v>
+        <v>463.6204755</v>
       </c>
     </row>
     <row r="652" spans="1:8">
@@ -25723,7 +25723,7 @@
         <v>16.9128</v>
       </c>
       <c r="H652">
-        <v>91.38325</v>
+        <v>91.38325489</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -25749,7 +25749,7 @@
         <v>79.87348</v>
       </c>
       <c r="H653">
-        <v>265.89975</v>
+        <v>265.8997464</v>
       </c>
     </row>
     <row r="654" spans="1:8">
@@ -25775,7 +25775,7 @@
         <v>81.62513</v>
       </c>
       <c r="H654">
-        <v>289.2572</v>
+        <v>289.2572032</v>
       </c>
     </row>
     <row r="655" spans="1:8">
@@ -25801,7 +25801,7 @@
         <v>99.79771</v>
       </c>
       <c r="H655">
-        <v>532.13512</v>
+        <v>532.1351165</v>
       </c>
     </row>
     <row r="656" spans="1:8">
@@ -25827,7 +25827,7 @@
         <v>95.5138</v>
       </c>
       <c r="H656">
-        <v>450.28279</v>
+        <v>412.4005134</v>
       </c>
     </row>
     <row r="657" spans="1:8">
@@ -25853,7 +25853,7 @@
         <v>78.8263</v>
       </c>
       <c r="H657">
-        <v>324.79621</v>
+        <v>284.3489093</v>
       </c>
     </row>
     <row r="658" spans="1:8">
@@ -25879,7 +25879,7 @@
         <v>53.49717</v>
       </c>
       <c r="H658">
-        <v>208.68053</v>
+        <v>208.6805263</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -25905,7 +25905,7 @@
         <v>51.72</v>
       </c>
       <c r="H659">
-        <v>249.99978</v>
+        <v>249.9997833</v>
       </c>
     </row>
     <row r="660" spans="1:8">
@@ -25931,7 +25931,7 @@
         <v>55.23315</v>
       </c>
       <c r="H660">
-        <v>287.2997</v>
+        <v>287.2996968</v>
       </c>
     </row>
     <row r="661" spans="1:8">
@@ -25957,7 +25957,7 @@
         <v>121.83405</v>
       </c>
       <c r="H661">
-        <v>333.87881</v>
+        <v>333.8788133</v>
       </c>
     </row>
     <row r="662" spans="1:8">
@@ -25983,7 +25983,7 @@
         <v>131.32985</v>
       </c>
       <c r="H662">
-        <v>337.80194</v>
+        <v>337.8019448</v>
       </c>
     </row>
     <row r="663" spans="1:8">
@@ -26009,7 +26009,7 @@
         <v>64.32980000000001</v>
       </c>
       <c r="H663">
-        <v>206.83177</v>
+        <v>206.8317658</v>
       </c>
     </row>
     <row r="664" spans="1:8">
@@ -26035,7 +26035,7 @@
         <v>37.46101</v>
       </c>
       <c r="H664">
-        <v>249.84971</v>
+        <v>249.8497064</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -26061,7 +26061,7 @@
         <v>37.55824</v>
       </c>
       <c r="H665">
-        <v>227.76193</v>
+        <v>227.7619313</v>
       </c>
     </row>
     <row r="666" spans="1:8">
@@ -26087,7 +26087,7 @@
         <v>14.01246</v>
       </c>
       <c r="H666">
-        <v>137.84075</v>
+        <v>137.8407454</v>
       </c>
     </row>
     <row r="667" spans="1:8">
@@ -26113,7 +26113,7 @@
         <v>37.80625</v>
       </c>
       <c r="H667">
-        <v>281.02157</v>
+        <v>281.0215729</v>
       </c>
     </row>
     <row r="668" spans="1:8">
@@ -26139,7 +26139,7 @@
         <v>133.6734</v>
       </c>
       <c r="H668">
-        <v>383.41355</v>
+        <v>383.4135514</v>
       </c>
     </row>
     <row r="669" spans="1:8">
@@ -26165,7 +26165,7 @@
         <v>147.79212</v>
       </c>
       <c r="H669">
-        <v>340.69641</v>
+        <v>267.4397489</v>
       </c>
     </row>
     <row r="670" spans="1:8">
@@ -26191,7 +26191,7 @@
         <v>111.63257</v>
       </c>
       <c r="H670">
-        <v>284.28914</v>
+        <v>284.2891407</v>
       </c>
     </row>
     <row r="671" spans="1:8">
@@ -26217,7 +26217,7 @@
         <v>78.93137</v>
       </c>
       <c r="H671">
-        <v>217.55306</v>
+        <v>155.0516626</v>
       </c>
     </row>
     <row r="672" spans="1:8">
@@ -26243,7 +26243,7 @@
         <v>139.07829</v>
       </c>
       <c r="H672">
-        <v>382.87829</v>
+        <v>382.8782853</v>
       </c>
     </row>
     <row r="673" spans="1:8">
@@ -26269,7 +26269,7 @@
         <v>113.8259</v>
       </c>
       <c r="H673">
-        <v>281.98353</v>
+        <v>281.9835334</v>
       </c>
     </row>
     <row r="674" spans="1:8">
@@ -26295,7 +26295,7 @@
         <v>76.48013</v>
       </c>
       <c r="H674">
-        <v>210.60565</v>
+        <v>210.6056513</v>
       </c>
     </row>
     <row r="675" spans="1:8">
@@ -26321,7 +26321,7 @@
         <v>14.75464</v>
       </c>
       <c r="H675">
-        <v>110.85059</v>
+        <v>118.1956363</v>
       </c>
     </row>
     <row r="676" spans="1:8">
@@ -26347,7 +26347,7 @@
         <v>16.3175</v>
       </c>
       <c r="H676">
-        <v>146.04842</v>
+        <v>146.0484237</v>
       </c>
     </row>
     <row r="677" spans="1:8">
@@ -26373,7 +26373,7 @@
         <v>223.75448</v>
       </c>
       <c r="H677">
-        <v>618.88486</v>
+        <v>618.8848589</v>
       </c>
     </row>
     <row r="678" spans="1:8">
@@ -26399,7 +26399,7 @@
         <v>115.23144</v>
       </c>
       <c r="H678">
-        <v>366.96477</v>
+        <v>366.9647748</v>
       </c>
     </row>
     <row r="679" spans="1:8">
@@ -26425,7 +26425,7 @@
         <v>134.833</v>
       </c>
       <c r="H679">
-        <v>330.04972</v>
+        <v>330.0497165</v>
       </c>
     </row>
     <row r="680" spans="1:8">
@@ -26451,7 +26451,7 @@
         <v>120.92755</v>
       </c>
       <c r="H680">
-        <v>305.57961</v>
+        <v>305.5796083</v>
       </c>
     </row>
     <row r="681" spans="1:8">
@@ -26477,7 +26477,7 @@
         <v>95.91905</v>
       </c>
       <c r="H681">
-        <v>244.45249</v>
+        <v>244.4524947</v>
       </c>
     </row>
     <row r="682" spans="1:8">
@@ -26503,7 +26503,7 @@
         <v>137.91924</v>
       </c>
       <c r="H682">
-        <v>385.41984</v>
+        <v>385.4198404</v>
       </c>
     </row>
     <row r="683" spans="1:8">
@@ -26529,7 +26529,7 @@
         <v>149.37796</v>
       </c>
       <c r="H683">
-        <v>339.54751</v>
+        <v>263.6641653</v>
       </c>
     </row>
     <row r="684" spans="1:8">
@@ -26555,7 +26555,7 @@
         <v>112.03041</v>
       </c>
       <c r="H684">
-        <v>281.92044</v>
+        <v>281.9204413</v>
       </c>
     </row>
     <row r="685" spans="1:8">
@@ -26581,7 +26581,7 @@
         <v>79.07877000000001</v>
       </c>
       <c r="H685">
-        <v>216.0455</v>
+        <v>216.0454984</v>
       </c>
     </row>
     <row r="686" spans="1:8">
@@ -26607,7 +26607,7 @@
         <v>23.2725</v>
       </c>
       <c r="H686">
-        <v>221.84666</v>
+        <v>221.8466589</v>
       </c>
     </row>
     <row r="687" spans="1:8">
@@ -26633,7 +26633,7 @@
         <v>24.90497</v>
       </c>
       <c r="H687">
-        <v>239.69616</v>
+        <v>225.0439514</v>
       </c>
     </row>
     <row r="688" spans="1:8">
@@ -26659,7 +26659,7 @@
         <v>22.01969</v>
       </c>
       <c r="H688">
-        <v>192.55594</v>
+        <v>181.4554469</v>
       </c>
     </row>
     <row r="689" spans="1:8">
@@ -26685,7 +26685,7 @@
         <v>74.39579999999999</v>
       </c>
       <c r="H689">
-        <v>340.20689</v>
+        <v>340.2068916</v>
       </c>
     </row>
     <row r="690" spans="1:8">
@@ -26711,7 +26711,7 @@
         <v>109.93589</v>
       </c>
       <c r="H690">
-        <v>321.6595</v>
+        <v>321.6594984</v>
       </c>
     </row>
     <row r="691" spans="1:8">
@@ -26737,7 +26737,7 @@
         <v>105.40153</v>
       </c>
       <c r="H691">
-        <v>305.5928</v>
+        <v>305.5927982</v>
       </c>
     </row>
     <row r="692" spans="1:8">
@@ -26763,7 +26763,7 @@
         <v>79.47075</v>
       </c>
       <c r="H692">
-        <v>598.09766</v>
+        <v>598.0976644</v>
       </c>
     </row>
     <row r="693" spans="1:8">
@@ -26789,7 +26789,7 @@
         <v>63.90048</v>
       </c>
       <c r="H693">
-        <v>385.70477</v>
+        <v>295.3707513</v>
       </c>
     </row>
     <row r="694" spans="1:8">
@@ -26815,7 +26815,7 @@
         <v>25.11221</v>
       </c>
       <c r="H694">
-        <v>311.74632</v>
+        <v>311.7463199</v>
       </c>
     </row>
     <row r="695" spans="1:8">
@@ -26841,7 +26841,7 @@
         <v>157.0003</v>
       </c>
       <c r="H695">
-        <v>338.57479</v>
+        <v>338.5747863</v>
       </c>
     </row>
     <row r="696" spans="1:8">
@@ -26867,7 +26867,7 @@
         <v>111.97853</v>
       </c>
       <c r="H696">
-        <v>271.66248</v>
+        <v>193.7232143</v>
       </c>
     </row>
     <row r="697" spans="1:8">
@@ -26893,7 +26893,7 @@
         <v>146.24413</v>
       </c>
       <c r="H697">
-        <v>795.84005</v>
+        <v>795.8400457</v>
       </c>
     </row>
     <row r="698" spans="1:8">
@@ -26919,7 +26919,7 @@
         <v>134.93228</v>
       </c>
       <c r="H698">
-        <v>520.86204</v>
+        <v>520.8620442</v>
       </c>
     </row>
     <row r="699" spans="1:8">
@@ -26945,7 +26945,7 @@
         <v>129.20633</v>
       </c>
       <c r="H699">
-        <v>635.62086</v>
+        <v>635.620855</v>
       </c>
     </row>
     <row r="700" spans="1:8">
@@ -26971,7 +26971,7 @@
         <v>125.99114</v>
       </c>
       <c r="H700">
-        <v>559.9747599999999</v>
+        <v>491.539474</v>
       </c>
     </row>
     <row r="701" spans="1:8">
@@ -26997,7 +26997,7 @@
         <v>86.65844</v>
       </c>
       <c r="H701">
-        <v>364.75629</v>
+        <v>364.7562923</v>
       </c>
     </row>
     <row r="702" spans="1:8">
@@ -27023,7 +27023,7 @@
         <v>38.44725</v>
       </c>
       <c r="H702">
-        <v>289.85108</v>
+        <v>289.8510754</v>
       </c>
     </row>
     <row r="703" spans="1:8">
@@ -27049,7 +27049,7 @@
         <v>46.94608</v>
       </c>
       <c r="H703">
-        <v>372.08519</v>
+        <v>372.0851877</v>
       </c>
     </row>
     <row r="704" spans="1:8">
@@ -27075,7 +27075,7 @@
         <v>38.63863</v>
       </c>
       <c r="H704">
-        <v>271.84987</v>
+        <v>230.075595</v>
       </c>
     </row>
     <row r="705" spans="1:8">
@@ -27101,7 +27101,7 @@
         <v>45.7165</v>
       </c>
       <c r="H705">
-        <v>503.82317</v>
+        <v>517.4836544999999</v>
       </c>
     </row>
     <row r="706" spans="1:8">
@@ -27127,7 +27127,7 @@
         <v>186.23118</v>
       </c>
       <c r="H706">
-        <v>545.4168100000001</v>
+        <v>545.4168149</v>
       </c>
     </row>
     <row r="707" spans="1:8">
@@ -27153,7 +27153,7 @@
         <v>103.14342</v>
       </c>
       <c r="H707">
-        <v>364.82055</v>
+        <v>364.8205506</v>
       </c>
     </row>
     <row r="708" spans="1:8">
@@ -27179,7 +27179,7 @@
         <v>127.68573</v>
       </c>
       <c r="H708">
-        <v>338.30213</v>
+        <v>338.302127</v>
       </c>
     </row>
     <row r="709" spans="1:8">
@@ -27205,7 +27205,7 @@
         <v>97.15412000000001</v>
       </c>
       <c r="H709">
-        <v>284.09713</v>
+        <v>226.2505497</v>
       </c>
     </row>
     <row r="710" spans="1:8">
@@ -27231,7 +27231,7 @@
         <v>75.55365</v>
       </c>
       <c r="H710">
-        <v>226.14874</v>
+        <v>177.8852909</v>
       </c>
     </row>
     <row r="711" spans="1:8">
@@ -27257,7 +27257,7 @@
         <v>179.05614</v>
       </c>
       <c r="H711">
-        <v>528.34522</v>
+        <v>528.3452225</v>
       </c>
     </row>
     <row r="712" spans="1:8">
@@ -27283,7 +27283,7 @@
         <v>90.67649</v>
       </c>
       <c r="H712">
-        <v>206.92788</v>
+        <v>206.9278845</v>
       </c>
     </row>
     <row r="713" spans="1:8">
@@ -27309,7 +27309,7 @@
         <v>257.34537</v>
       </c>
       <c r="H713">
-        <v>337.37524</v>
+        <v>301.0119675</v>
       </c>
     </row>
     <row r="714" spans="1:8">
@@ -27335,7 +27335,7 @@
         <v>216.44399</v>
       </c>
       <c r="H714">
-        <v>409.14567</v>
+        <v>366.1224191</v>
       </c>
     </row>
     <row r="715" spans="1:8">
@@ -27361,7 +27361,7 @@
         <v>30.57603</v>
       </c>
       <c r="H715">
-        <v>136.48086</v>
+        <v>136.480862</v>
       </c>
     </row>
     <row r="716" spans="1:8">
@@ -27387,7 +27387,7 @@
         <v>68.21427</v>
       </c>
       <c r="H716">
-        <v>197.31796</v>
+        <v>114.6541823</v>
       </c>
     </row>
     <row r="717" spans="1:8">
@@ -27413,7 +27413,7 @@
         <v>99.9575</v>
       </c>
       <c r="H717">
-        <v>365.57757</v>
+        <v>365.5775681</v>
       </c>
     </row>
     <row r="718" spans="1:8">
@@ -27439,7 +27439,7 @@
         <v>123.21462</v>
       </c>
       <c r="H718">
-        <v>337.02979</v>
+        <v>337.029785</v>
       </c>
     </row>
     <row r="719" spans="1:8">
@@ -27465,7 +27465,7 @@
         <v>94.35834</v>
       </c>
       <c r="H719">
-        <v>283.85003</v>
+        <v>283.8500282</v>
       </c>
     </row>
     <row r="720" spans="1:8">
@@ -27491,7 +27491,7 @@
         <v>73.7465</v>
       </c>
       <c r="H720">
-        <v>226.11651</v>
+        <v>226.1165143</v>
       </c>
     </row>
     <row r="721" spans="1:8">
@@ -27517,7 +27517,7 @@
         <v>17.89416</v>
       </c>
       <c r="H721">
-        <v>140.40894</v>
+        <v>133.8336302</v>
       </c>
     </row>
     <row r="722" spans="1:8">
@@ -27543,7 +27543,7 @@
         <v>20.484</v>
       </c>
       <c r="H722">
-        <v>197.18228</v>
+        <v>197.1822809</v>
       </c>
     </row>
     <row r="723" spans="1:8">
@@ -27569,7 +27569,7 @@
         <v>159.24928</v>
       </c>
       <c r="H723">
-        <v>753.49329</v>
+        <v>753.4932896</v>
       </c>
     </row>
     <row r="724" spans="1:8">
@@ -27595,7 +27595,7 @@
         <v>150.74453</v>
       </c>
       <c r="H724">
-        <v>531.18623</v>
+        <v>467.3721501</v>
       </c>
     </row>
     <row r="725" spans="1:8">
@@ -27621,7 +27621,7 @@
         <v>135.80381</v>
       </c>
       <c r="H725">
-        <v>489.29343</v>
+        <v>489.2934281</v>
       </c>
     </row>
     <row r="726" spans="1:8">
@@ -27647,7 +27647,7 @@
         <v>102.22138</v>
       </c>
       <c r="H726">
-        <v>341.17434</v>
+        <v>341.174339</v>
       </c>
     </row>
     <row r="727" spans="1:8">
@@ -27673,7 +27673,7 @@
         <v>112.24472</v>
       </c>
       <c r="H727">
-        <v>369.95542</v>
+        <v>369.9554196</v>
       </c>
     </row>
     <row r="728" spans="1:8">
@@ -27699,7 +27699,7 @@
         <v>134.25872</v>
       </c>
       <c r="H728">
-        <v>339.352</v>
+        <v>339.3520031</v>
       </c>
     </row>
     <row r="729" spans="1:8">
@@ -27725,7 +27725,7 @@
         <v>102.92408</v>
       </c>
       <c r="H729">
-        <v>285.54139</v>
+        <v>285.5413863</v>
       </c>
     </row>
     <row r="730" spans="1:8">
@@ -27751,7 +27751,7 @@
         <v>78.16115000000001</v>
       </c>
       <c r="H730">
-        <v>225.3644</v>
+        <v>160.4356721</v>
       </c>
     </row>
     <row r="731" spans="1:8">
@@ -27777,7 +27777,7 @@
         <v>79.2642</v>
       </c>
       <c r="H731">
-        <v>327.29974</v>
+        <v>280.8180242</v>
       </c>
     </row>
     <row r="732" spans="1:8">
@@ -27803,7 +27803,7 @@
         <v>66.71281</v>
       </c>
       <c r="H732">
-        <v>259.17306</v>
+        <v>233.2784491</v>
       </c>
     </row>
     <row r="733" spans="1:8">
@@ -27829,7 +27829,7 @@
         <v>158.45327</v>
       </c>
       <c r="H733">
-        <v>357.5849</v>
+        <v>357.5848954</v>
       </c>
     </row>
     <row r="734" spans="1:8">
@@ -27855,7 +27855,7 @@
         <v>143.93072</v>
       </c>
       <c r="H734">
-        <v>340.04404</v>
+        <v>272.5061559</v>
       </c>
     </row>
     <row r="735" spans="1:8">
@@ -27881,7 +27881,7 @@
         <v>110.24136</v>
       </c>
       <c r="H735">
-        <v>285.88555</v>
+        <v>285.8855517</v>
       </c>
     </row>
     <row r="736" spans="1:8">
@@ -27907,7 +27907,7 @@
         <v>79.79988</v>
       </c>
       <c r="H736">
-        <v>221.20266</v>
+        <v>155.2755475</v>
       </c>
     </row>
     <row r="737" spans="1:8">
@@ -27933,7 +27933,7 @@
         <v>144.49568</v>
       </c>
       <c r="H737">
-        <v>288.26873</v>
+        <v>288.2687332</v>
       </c>
     </row>
     <row r="738" spans="1:8">
@@ -27959,7 +27959,7 @@
         <v>101.10736</v>
       </c>
       <c r="H738">
-        <v>233.5264</v>
+        <v>233.5263969</v>
       </c>
     </row>
     <row r="739" spans="1:8">
@@ -27985,7 +27985,7 @@
         <v>70.68365</v>
       </c>
       <c r="H739">
-        <v>182.34911</v>
+        <v>182.3491127</v>
       </c>
     </row>
     <row r="740" spans="1:8">
@@ -28011,7 +28011,7 @@
         <v>78.71991</v>
       </c>
       <c r="H740">
-        <v>393.23876</v>
+        <v>393.2387622</v>
       </c>
     </row>
     <row r="741" spans="1:8">
@@ -28037,7 +28037,7 @@
         <v>132.22992</v>
       </c>
       <c r="H741">
-        <v>514.43026</v>
+        <v>514.4302586</v>
       </c>
     </row>
     <row r="742" spans="1:8">
@@ -28063,7 +28063,7 @@
         <v>143.58227</v>
       </c>
       <c r="H742">
-        <v>426.65613</v>
+        <v>426.6561315</v>
       </c>
     </row>
     <row r="743" spans="1:8">
@@ -28089,7 +28089,7 @@
         <v>109.87243</v>
       </c>
       <c r="H743">
-        <v>358.70952</v>
+        <v>358.7095162</v>
       </c>
     </row>
     <row r="744" spans="1:8">
@@ -28115,7 +28115,7 @@
         <v>79.8266</v>
       </c>
       <c r="H744">
-        <v>263.40971</v>
+        <v>183.6896879</v>
       </c>
     </row>
     <row r="745" spans="1:8">
@@ -28141,7 +28141,7 @@
         <v>82.08486000000001</v>
       </c>
       <c r="H745">
-        <v>298.6288</v>
+        <v>298.6288048</v>
       </c>
     </row>
     <row r="746" spans="1:8">
@@ -28167,7 +28167,7 @@
         <v>113.31813</v>
       </c>
       <c r="H746">
-        <v>278.94163</v>
+        <v>278.9416347</v>
       </c>
     </row>
     <row r="747" spans="1:8">
@@ -28193,7 +28193,7 @@
         <v>73.55758</v>
       </c>
       <c r="H747">
-        <v>204.93405</v>
+        <v>204.9340458</v>
       </c>
     </row>
     <row r="748" spans="1:8">
@@ -28219,7 +28219,7 @@
         <v>120.48745</v>
       </c>
       <c r="H748">
-        <v>252.85099</v>
+        <v>252.8509884</v>
       </c>
     </row>
     <row r="749" spans="1:8">
@@ -28245,7 +28245,7 @@
         <v>226.22168</v>
       </c>
       <c r="H749">
-        <v>780.49938</v>
+        <v>780.4993785</v>
       </c>
     </row>
     <row r="750" spans="1:8">
@@ -28271,7 +28271,7 @@
         <v>107.34684</v>
       </c>
       <c r="H750">
-        <v>282.4475</v>
+        <v>282.4475002</v>
       </c>
     </row>
     <row r="751" spans="1:8">
@@ -28297,7 +28297,7 @@
         <v>61.88545</v>
       </c>
       <c r="H751">
-        <v>249.2483</v>
+        <v>249.2482952</v>
       </c>
     </row>
     <row r="752" spans="1:8">
@@ -28323,7 +28323,7 @@
         <v>91.797</v>
       </c>
       <c r="H752">
-        <v>1169.25936</v>
+        <v>1169.259357</v>
       </c>
     </row>
     <row r="753" spans="1:8">
@@ -28349,7 +28349,7 @@
         <v>115.6495</v>
       </c>
       <c r="H753">
-        <v>473.3098</v>
+        <v>473.3097979</v>
       </c>
     </row>
     <row r="754" spans="1:8">
@@ -28375,7 +28375,7 @@
         <v>59.41018</v>
       </c>
       <c r="H754">
-        <v>252.74534</v>
+        <v>235.5652654</v>
       </c>
     </row>
     <row r="755" spans="1:8">
@@ -28401,7 +28401,7 @@
         <v>100.9944</v>
       </c>
       <c r="H755">
-        <v>305.574</v>
+        <v>305.5739997</v>
       </c>
     </row>
     <row r="756" spans="1:8">
@@ -28427,7 +28427,7 @@
         <v>104.52988</v>
       </c>
       <c r="H756">
-        <v>402.30735</v>
+        <v>402.3073462</v>
       </c>
     </row>
     <row r="757" spans="1:8">
@@ -28453,7 +28453,7 @@
         <v>64.48616</v>
       </c>
       <c r="H757">
-        <v>228.21558</v>
+        <v>228.215585</v>
       </c>
     </row>
     <row r="758" spans="1:8">
@@ -28479,7 +28479,7 @@
         <v>61.09795</v>
       </c>
       <c r="H758">
-        <v>237.07348</v>
+        <v>231.4917665</v>
       </c>
     </row>
     <row r="759" spans="1:8">
@@ -28505,7 +28505,7 @@
         <v>90.2997</v>
       </c>
       <c r="H759">
-        <v>383.76105</v>
+        <v>383.761051</v>
       </c>
     </row>
     <row r="760" spans="1:8">
@@ -28531,7 +28531,7 @@
         <v>119.9839</v>
       </c>
       <c r="H760">
-        <v>414.7637</v>
+        <v>417.9045568</v>
       </c>
     </row>
     <row r="761" spans="1:8">
@@ -28557,7 +28557,7 @@
         <v>66.56992</v>
       </c>
       <c r="H761">
-        <v>316.52054</v>
+        <v>261.0615738</v>
       </c>
     </row>
     <row r="762" spans="1:8">
@@ -28583,7 +28583,7 @@
         <v>101.23335</v>
       </c>
       <c r="H762">
-        <v>403.29079</v>
+        <v>403.2907934</v>
       </c>
     </row>
     <row r="763" spans="1:8">
@@ -28609,7 +28609,7 @@
         <v>62.1894</v>
       </c>
       <c r="H763">
-        <v>235.06545</v>
+        <v>233.5416747</v>
       </c>
     </row>
     <row r="764" spans="1:8">
@@ -28635,7 +28635,7 @@
         <v>60.93496</v>
       </c>
       <c r="H764">
-        <v>275.38066</v>
+        <v>222.3368339</v>
       </c>
     </row>
     <row r="765" spans="1:8">
@@ -28661,7 +28661,7 @@
         <v>86.47487</v>
       </c>
       <c r="H765">
-        <v>297.50699</v>
+        <v>297.5069888</v>
       </c>
     </row>
     <row r="766" spans="1:8">
@@ -28687,7 +28687,7 @@
         <v>104.00339</v>
       </c>
       <c r="H766">
-        <v>482.0921</v>
+        <v>482.0921027</v>
       </c>
     </row>
     <row r="767" spans="1:8">
